--- a/res_winter_rb.xlsx
+++ b/res_winter_rb.xlsx
@@ -4,7 +4,7 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
@@ -53,18 +53,18 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyAlignment="1" borderId="1" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -587,13 +587,13 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>3000.000000000001</v>
+        <v>2986.570612333543</v>
       </c>
       <c r="L2" t="n">
-        <v>2400.000000000001</v>
+        <v>2389.256489866835</v>
       </c>
       <c r="M2" t="n">
-        <v>6000.000000000002</v>
+        <v>5973.141224667086</v>
       </c>
       <c r="N2" t="n">
         <v>571.3924</v>
@@ -1120,7 +1120,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>753.1270348803744</v>
+        <v>737.9089489947985</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -1129,7 +1129,7 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>561.7601741959601</v>
+        <v>550.4089489947985</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -1138,7 +1138,7 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>191.3668606844143</v>
+        <v>187.5</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -1156,10 +1156,10 @@
         <v>6000</v>
       </c>
       <c r="N9" t="n">
-        <v>947.7954258040398</v>
+        <v>959.1466510052014</v>
       </c>
       <c r="O9" t="n">
-        <v>20.96544656979571</v>
+        <v>21.21653820727094</v>
       </c>
       <c r="P9" t="n">
         <v>277.41</v>
@@ -1200,7 +1200,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.474161863343995e-13</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -1209,7 +1209,7 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>3.337293486127834e-13</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>1.13686837721616e-13</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -1236,7 +1236,7 @@
         <v>6000</v>
       </c>
       <c r="N10" t="n">
-        <v>1531.017599999999</v>
+        <v>1531.0176</v>
       </c>
       <c r="O10" t="n">
         <v>33.90019595903681</v>
@@ -1360,7 +1360,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>737.9089489947985</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
@@ -1369,7 +1369,7 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>550.4089489947985</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -1378,7 +1378,7 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>187.5</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1396,10 +1396,10 @@
         <v>6000</v>
       </c>
       <c r="N12" t="n">
-        <v>1555.848</v>
+        <v>1005.439051005201</v>
       </c>
       <c r="O12" t="n">
-        <v>34.86689450389375</v>
+        <v>22.53210938439578</v>
       </c>
       <c r="P12" t="n">
         <v>277.9299999999999</v>
@@ -1440,7 +1440,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>662.9089489947985</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>475.4089489947985</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -1458,7 +1458,7 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>187.5</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -1476,10 +1476,10 @@
         <v>6000</v>
       </c>
       <c r="N13" t="n">
-        <v>1081.774651005201</v>
+        <v>1557.1836</v>
       </c>
       <c r="O13" t="n">
-        <v>24.32252384149298</v>
+        <v>35.01157584103878</v>
       </c>
       <c r="P13" t="n">
         <v>278.06</v>
@@ -1520,7 +1520,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>737.9089489947985</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
@@ -1529,7 +1529,7 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>550.4089489947985</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -1538,7 +1538,7 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>187.5</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -1556,10 +1556,10 @@
         <v>6000</v>
       </c>
       <c r="N14" t="n">
-        <v>1000.138651005202</v>
+        <v>1550.5476</v>
       </c>
       <c r="O14" t="n">
-        <v>22.59562046891165</v>
+        <v>35.03072804292574</v>
       </c>
       <c r="P14" t="n">
         <v>278.25</v>
@@ -1600,7 +1600,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>662.9089489947985</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
@@ -1609,7 +1609,7 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>475.4089489947985</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -1618,7 +1618,7 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>187.5</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -1636,10 +1636,10 @@
         <v>6000</v>
       </c>
       <c r="N15" t="n">
-        <v>1555.5624</v>
+        <v>1080.153451005201</v>
       </c>
       <c r="O15" t="n">
-        <v>35.27852360028348</v>
+        <v>24.49674729423561</v>
       </c>
       <c r="P15" t="n">
         <v>278.4</v>
@@ -1680,7 +1680,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>737.9089489947985</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
@@ -1689,7 +1689,7 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>550.4089489947985</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -1698,7 +1698,7 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>187.5</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -1716,10 +1716,10 @@
         <v>6000</v>
       </c>
       <c r="N16" t="n">
-        <v>1559.0232</v>
+        <v>1008.614251005201</v>
       </c>
       <c r="O16" t="n">
-        <v>35.35701091424522</v>
+        <v>22.87431327580896</v>
       </c>
       <c r="P16" t="n">
         <v>278.4</v>
@@ -1760,7 +1760,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1122.561121350132</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
@@ -1769,7 +1769,7 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>818.2651637539703</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -1778,7 +1778,7 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>304.2959575961622</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -1796,10 +1796,10 @@
         <v>6000</v>
       </c>
       <c r="N17" t="n">
-        <v>751.2916362460295</v>
+        <v>1569.5568</v>
       </c>
       <c r="O17" t="n">
-        <v>16.99514517169018</v>
+        <v>35.50531429379328</v>
       </c>
       <c r="P17" t="n">
         <v>278.3</v>
@@ -1920,7 +1920,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>662.9089489947985</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -1929,7 +1929,7 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>475.4089489947985</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -1938,7 +1938,7 @@
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>187.5</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -1956,10 +1956,10 @@
         <v>6000</v>
       </c>
       <c r="N19" t="n">
-        <v>1579.3092</v>
+        <v>1103.900251005201</v>
       </c>
       <c r="O19" t="n">
-        <v>35.55401170643852</v>
+        <v>24.85142393077895</v>
       </c>
       <c r="P19" t="n">
         <v>278.11</v>
@@ -2000,7 +2000,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>745.2729291608771</v>
+        <v>737.9089489947985</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
@@ -2009,7 +2009,7 @@
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>536.8445391444977</v>
+        <v>550.4089489947985</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -2018,7 +2018,7 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>208.4283900163794</v>
+        <v>187.5</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -2036,10 +2036,10 @@
         <v>6000</v>
       </c>
       <c r="N20" t="n">
-        <v>1014.853860855502</v>
+        <v>1001.289451005201</v>
       </c>
       <c r="O20" t="n">
-        <v>22.84677759692709</v>
+        <v>22.54141042334986</v>
       </c>
       <c r="P20" t="n">
         <v>278.11</v>
@@ -2240,7 +2240,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>662.9089489947989</v>
+        <v>662.9089489947985</v>
       </c>
       <c r="C23" t="n">
         <v>0</v>
@@ -2249,7 +2249,7 @@
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>475.4089489947989</v>
+        <v>475.4089489947985</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -2258,7 +2258,7 @@
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>187.5000000000001</v>
+        <v>187.5</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -2267,19 +2267,19 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>3000.000000000001</v>
+        <v>3000</v>
       </c>
       <c r="L23" t="n">
-        <v>2400.000000000001</v>
+        <v>2400</v>
       </c>
       <c r="M23" t="n">
-        <v>6000.000000000002</v>
+        <v>6000</v>
       </c>
       <c r="N23" t="n">
-        <v>932.6326510052013</v>
+        <v>932.6326510052018</v>
       </c>
       <c r="O23" t="n">
-        <v>20.90050201143371</v>
+        <v>20.90050201143372</v>
       </c>
       <c r="P23" t="n">
         <v>277.9299999999999</v>
@@ -2480,7 +2480,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>929.3513128961123</v>
+        <v>784.0466815706947</v>
       </c>
       <c r="C26" t="n">
         <v>0</v>
@@ -2489,7 +2489,7 @@
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>675.2946575894578</v>
+        <v>566.7456994643405</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -2498,7 +2498,7 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>254.0566553066545</v>
+        <v>217.3009821063542</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -2516,10 +2516,10 @@
         <v>6000</v>
       </c>
       <c r="N26" t="n">
-        <v>717.5765424105421</v>
+        <v>826.1255005356593</v>
       </c>
       <c r="O26" t="n">
-        <v>15.9683236141428</v>
+        <v>18.38387761970869</v>
       </c>
       <c r="P26" t="n">
         <v>277.65</v>
@@ -2720,7 +2720,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="n">
-        <v>666.2357331899759</v>
+        <v>0</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
@@ -2729,7 +2729,7 @@
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>478.7357331899759</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -2738,7 +2738,7 @@
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>187.5</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -2756,10 +2756,10 @@
         <v>6000</v>
       </c>
       <c r="N29" t="n">
-        <v>906.1806668100241</v>
+        <v>1384.9164</v>
       </c>
       <c r="O29" t="n">
-        <v>20.09993992979786</v>
+        <v>30.71874899492611</v>
       </c>
       <c r="P29" t="n">
         <v>277.52</v>
@@ -2800,7 +2800,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>750.9313694207765</v>
       </c>
       <c r="C30" t="n">
         <v>0</v>
@@ -2809,7 +2809,7 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>542.0071030474701</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -2818,7 +2818,7 @@
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>208.9242663733064</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -2836,10 +2836,10 @@
         <v>6000</v>
       </c>
       <c r="N30" t="n">
-        <v>1373.3832</v>
+        <v>831.3760969525297</v>
       </c>
       <c r="O30" t="n">
-        <v>30.44014406826617</v>
+        <v>18.42690966814494</v>
       </c>
       <c r="P30" t="n">
         <v>277.49</v>
@@ -2880,7 +2880,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>-3.19582712600225e-12</v>
       </c>
       <c r="C31" t="n">
         <v>0</v>
@@ -2889,7 +2889,7 @@
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>-2.387423592153937e-12</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -2898,7 +2898,7 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>-8.08403533848313e-13</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
@@ -2916,10 +2916,10 @@
         <v>6000</v>
       </c>
       <c r="N31" t="n">
-        <v>1422.078</v>
+        <v>1422.078000000002</v>
       </c>
       <c r="O31" t="n">
-        <v>31.47234701781562</v>
+        <v>31.47234701781568</v>
       </c>
       <c r="P31" t="n">
         <v>277.4299999999999</v>
@@ -3040,7 +3040,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="n">
-        <v>847.975750970432</v>
+        <v>666.3394231437037</v>
       </c>
       <c r="C33" t="n">
         <v>0</v>
@@ -3049,7 +3049,7 @@
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>614.5035294381737</v>
+        <v>478.8131941514231</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -3058,7 +3058,7 @@
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>233.4722215322583</v>
+        <v>187.5262289922806</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
@@ -3076,10 +3076,10 @@
         <v>6000</v>
       </c>
       <c r="N33" t="n">
-        <v>959.4800705618261</v>
+        <v>1095.170405848577</v>
       </c>
       <c r="O33" t="n">
-        <v>21.2080804699655</v>
+        <v>24.20734188044267</v>
       </c>
       <c r="P33" t="n">
         <v>277.38</v>
@@ -3120,7 +3120,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="n">
-        <v>741.235733189976</v>
+        <v>741.2357331899756</v>
       </c>
       <c r="C34" t="n">
         <v>0</v>
@@ -3129,7 +3129,7 @@
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>553.735733189976</v>
+        <v>553.7357331899757</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -3138,7 +3138,7 @@
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>187.5</v>
+        <v>187.4999999999999</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
@@ -3159,7 +3159,7 @@
         <v>1019.878266810024</v>
       </c>
       <c r="O34" t="n">
-        <v>22.63880725438453</v>
+        <v>22.63880725438454</v>
       </c>
       <c r="P34" t="n">
         <v>277.55</v>
@@ -3313,7 +3313,7 @@
         <v>2400</v>
       </c>
       <c r="M36" t="n">
-        <v>6000.000000000001</v>
+        <v>6000</v>
       </c>
       <c r="N36" t="n">
         <v>1572.7992</v>
@@ -3387,13 +3387,13 @@
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>3000</v>
+        <v>2843.510625068056</v>
       </c>
       <c r="L37" t="n">
-        <v>2400</v>
+        <v>2274.808500054445</v>
       </c>
       <c r="M37" t="n">
-        <v>6000.000000000001</v>
+        <v>5687.021250136112</v>
       </c>
       <c r="N37" t="n">
         <v>1586.046</v>
@@ -3467,13 +3467,13 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>2843.510625068056</v>
+        <v>3000</v>
       </c>
       <c r="L38" t="n">
-        <v>2274.808500054445</v>
+        <v>2400</v>
       </c>
       <c r="M38" t="n">
-        <v>5687.021250136112</v>
+        <v>6000.000000000001</v>
       </c>
       <c r="N38" t="n">
         <v>1613.9928</v>
@@ -3760,7 +3760,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="n">
-        <v>912.4010874117926</v>
+        <v>912.4010874117912</v>
       </c>
       <c r="C42" t="n">
         <v>0</v>
@@ -3769,7 +3769,7 @@
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>662.6320927453401</v>
+        <v>662.632092745339</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>249.7689946664525</v>
+        <v>249.7689946664522</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -3796,10 +3796,10 @@
         <v>6000</v>
       </c>
       <c r="N42" t="n">
-        <v>889.6207072546597</v>
+        <v>889.6207072546607</v>
       </c>
       <c r="O42" t="n">
-        <v>20.37843791672568</v>
+        <v>20.3784379167257</v>
       </c>
       <c r="P42" t="n">
         <v>278.79</v>
@@ -3840,7 +3840,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="n">
-        <v>741.2357331899755</v>
+        <v>741.2357331899775</v>
       </c>
       <c r="C43" t="n">
         <v>0</v>
@@ -3849,7 +3849,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>553.7357331899756</v>
+        <v>553.7357331899771</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -3858,7 +3858,7 @@
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>187.4999999999999</v>
+        <v>187.5000000000004</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
@@ -3876,10 +3876,10 @@
         <v>6000</v>
       </c>
       <c r="N43" t="n">
-        <v>988.5714668100242</v>
+        <v>988.5714668100227</v>
       </c>
       <c r="O43" t="n">
-        <v>22.50589565873702</v>
+        <v>22.50589565873699</v>
       </c>
       <c r="P43" t="n">
         <v>278.55</v>
@@ -4400,7 +4400,7 @@
         <v>48</v>
       </c>
       <c r="B50" t="n">
-        <v>667.4339197923005</v>
+        <v>1156.671011549335</v>
       </c>
       <c r="C50" t="n">
         <v>0</v>
@@ -4409,7 +4409,7 @@
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>479.9339197923005</v>
+        <v>845.6152953313767</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -4418,7 +4418,7 @@
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>187.5</v>
+        <v>311.0557162179584</v>
       </c>
       <c r="I50" t="n">
         <v>0</v>
@@ -4436,10 +4436,10 @@
         <v>6000</v>
       </c>
       <c r="N50" t="n">
-        <v>911.5932802076995</v>
+        <v>545.9119046686233</v>
       </c>
       <c r="O50" t="n">
-        <v>20.12958194170857</v>
+        <v>12.05469440875814</v>
       </c>
       <c r="P50" t="n">
         <v>277.34</v>
@@ -4480,7 +4480,7 @@
         <v>49</v>
       </c>
       <c r="B51" t="n">
-        <v>742.4339197923005</v>
+        <v>0</v>
       </c>
       <c r="C51" t="n">
         <v>0</v>
@@ -4489,7 +4489,7 @@
         <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>554.9339197923005</v>
+        <v>0</v>
       </c>
       <c r="F51" t="n">
         <v>0</v>
@@ -4498,7 +4498,7 @@
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>187.5</v>
+        <v>0</v>
       </c>
       <c r="I51" t="n">
         <v>0</v>
@@ -4516,10 +4516,10 @@
         <v>6000</v>
       </c>
       <c r="N51" t="n">
-        <v>820.3980802076996</v>
+        <v>1375.332</v>
       </c>
       <c r="O51" t="n">
-        <v>18.12934269283907</v>
+        <v>30.39239821004367</v>
       </c>
       <c r="P51" t="n">
         <v>277.37</v>
@@ -4560,7 +4560,7 @@
         <v>50</v>
       </c>
       <c r="B52" t="n">
-        <v>0</v>
+        <v>667.4339197923005</v>
       </c>
       <c r="C52" t="n">
         <v>0</v>
@@ -4569,7 +4569,7 @@
         <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>0</v>
+        <v>479.9339197923004</v>
       </c>
       <c r="F52" t="n">
         <v>0</v>
@@ -4578,7 +4578,7 @@
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>0</v>
+        <v>187.5</v>
       </c>
       <c r="I52" t="n">
         <v>0</v>
@@ -4596,10 +4596,10 @@
         <v>6000</v>
       </c>
       <c r="N52" t="n">
-        <v>1362.5472</v>
+        <v>882.6132802076995</v>
       </c>
       <c r="O52" t="n">
-        <v>30.04265799410192</v>
+        <v>19.46064614740125</v>
       </c>
       <c r="P52" t="n">
         <v>277.28</v>
@@ -4640,7 +4640,7 @@
         <v>51</v>
       </c>
       <c r="B53" t="n">
-        <v>667.4339197923005</v>
+        <v>0</v>
       </c>
       <c r="C53" t="n">
         <v>0</v>
@@ -4649,7 +4649,7 @@
         <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>479.9339197923004</v>
+        <v>0</v>
       </c>
       <c r="F53" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>187.5</v>
+        <v>0</v>
       </c>
       <c r="I53" t="n">
         <v>0</v>
@@ -4676,10 +4676,10 @@
         <v>6000</v>
       </c>
       <c r="N53" t="n">
-        <v>884.7720802076994</v>
+        <v>1364.706</v>
       </c>
       <c r="O53" t="n">
-        <v>19.49857205493402</v>
+        <v>30.07533676758217</v>
       </c>
       <c r="P53" t="n">
         <v>277.26</v>
@@ -4880,7 +4880,7 @@
         <v>54</v>
       </c>
       <c r="B56" t="n">
-        <v>742.4339197923005</v>
+        <v>742.4339197922997</v>
       </c>
       <c r="C56" t="n">
         <v>0</v>
@@ -4889,7 +4889,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>554.9339197923005</v>
+        <v>554.9339197922999</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -4898,7 +4898,7 @@
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>187.5</v>
+        <v>187.4999999999998</v>
       </c>
       <c r="I56" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         <v>6000</v>
       </c>
       <c r="N56" t="n">
-        <v>871.6296802076997</v>
+        <v>871.6296802077003</v>
       </c>
       <c r="O56" t="n">
-        <v>19.3142881247032</v>
+        <v>19.31428812470321</v>
       </c>
       <c r="P56" t="n">
         <v>277.48</v>
@@ -4960,7 +4960,7 @@
         <v>55</v>
       </c>
       <c r="B57" t="n">
-        <v>742.5829869206714</v>
+        <v>995.7798149559416</v>
       </c>
       <c r="C57" t="n">
         <v>0</v>
@@ -4969,7 +4969,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>555.0453403560083</v>
+        <v>744.2978846092358</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -4978,7 +4978,7 @@
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>187.5376465646631</v>
+        <v>251.4819303467058</v>
       </c>
       <c r="I57" t="n">
         <v>0</v>
@@ -4996,10 +4996,10 @@
         <v>6000</v>
       </c>
       <c r="N57" t="n">
-        <v>930.2342596439915</v>
+        <v>740.9817153907641</v>
       </c>
       <c r="O57" t="n">
-        <v>20.74216533015199</v>
+        <v>16.52225241966138</v>
       </c>
       <c r="P57" t="n">
         <v>277.73</v>
@@ -5120,7 +5120,7 @@
         <v>57</v>
       </c>
       <c r="B59" t="n">
-        <v>667.4339197923005</v>
+        <v>667.4339197923003</v>
       </c>
       <c r="C59" t="n">
         <v>0</v>
@@ -5129,7 +5129,7 @@
         <v>0</v>
       </c>
       <c r="E59" t="n">
-        <v>479.9339197923005</v>
+        <v>479.9339197923003</v>
       </c>
       <c r="F59" t="n">
         <v>0</v>
@@ -5156,7 +5156,7 @@
         <v>6000</v>
       </c>
       <c r="N59" t="n">
-        <v>1056.560480207699</v>
+        <v>1056.5604802077</v>
       </c>
       <c r="O59" t="n">
         <v>23.76162105493534</v>
@@ -5200,7 +5200,7 @@
         <v>58</v>
       </c>
       <c r="B60" t="n">
-        <v>742.4339197923005</v>
+        <v>742.4339197922957</v>
       </c>
       <c r="C60" t="n">
         <v>0</v>
@@ -5209,7 +5209,7 @@
         <v>0</v>
       </c>
       <c r="E60" t="n">
-        <v>554.9339197923005</v>
+        <v>554.9339197922969</v>
       </c>
       <c r="F60" t="n">
         <v>0</v>
@@ -5218,7 +5218,7 @@
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>187.5</v>
+        <v>187.4999999999988</v>
       </c>
       <c r="I60" t="n">
         <v>0</v>
@@ -5236,10 +5236,10 @@
         <v>6000</v>
       </c>
       <c r="N60" t="n">
-        <v>1054.674080207699</v>
+        <v>1054.674080207703</v>
       </c>
       <c r="O60" t="n">
-        <v>23.80955679561361</v>
+        <v>23.80955679561368</v>
       </c>
       <c r="P60" t="n">
         <v>278.22</v>
@@ -5280,7 +5280,7 @@
         <v>59</v>
       </c>
       <c r="B61" t="n">
-        <v>742.4339197923003</v>
+        <v>742.4339197923005</v>
       </c>
       <c r="C61" t="n">
         <v>0</v>
@@ -5289,7 +5289,7 @@
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>554.9339197923003</v>
+        <v>554.9339197923005</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
@@ -5520,7 +5520,7 @@
         <v>62</v>
       </c>
       <c r="B64" t="n">
-        <v>760.1172661791234</v>
+        <v>760.1172661791545</v>
       </c>
       <c r="C64" t="n">
         <v>0</v>
@@ -5529,7 +5529,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>549.2102975799638</v>
+        <v>549.2102975799871</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -5538,7 +5538,7 @@
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>210.9069685991595</v>
+        <v>210.9069685991674</v>
       </c>
       <c r="I64" t="n">
         <v>0</v>
@@ -5556,10 +5556,10 @@
         <v>6000</v>
       </c>
       <c r="N64" t="n">
-        <v>1001.799302420036</v>
+        <v>1001.799302420012</v>
       </c>
       <c r="O64" t="n">
-        <v>23.1208909193096</v>
+        <v>23.12089091930906</v>
       </c>
       <c r="P64" t="n">
         <v>279.08</v>
@@ -5760,7 +5760,7 @@
         <v>65</v>
       </c>
       <c r="B67" t="n">
-        <v>865.9861747256231</v>
+        <v>865.9861747255941</v>
       </c>
       <c r="C67" t="n">
         <v>0</v>
@@ -5769,7 +5769,7 @@
         <v>0</v>
       </c>
       <c r="E67" t="n">
-        <v>628.3422537549691</v>
+        <v>628.3422537549474</v>
       </c>
       <c r="F67" t="n">
         <v>0</v>
@@ -5778,7 +5778,7 @@
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>237.643920970654</v>
+        <v>237.6439209706467</v>
       </c>
       <c r="I67" t="n">
         <v>0</v>
@@ -5796,10 +5796,10 @@
         <v>6000</v>
       </c>
       <c r="N67" t="n">
-        <v>895.1657462450305</v>
+        <v>895.1657462450522</v>
       </c>
       <c r="O67" t="n">
-        <v>20.77312168579289</v>
+        <v>20.7731216857934</v>
       </c>
       <c r="P67" t="n">
         <v>279.29</v>
@@ -6107,13 +6107,13 @@
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>3000.000000000002</v>
+        <v>3000</v>
       </c>
       <c r="L71" t="n">
-        <v>2400.000000000001</v>
+        <v>2400</v>
       </c>
       <c r="M71" t="n">
-        <v>6000.000000000004</v>
+        <v>6000</v>
       </c>
       <c r="N71" t="n">
         <v>856.2876802076994</v>
@@ -6320,7 +6320,7 @@
         <v>72</v>
       </c>
       <c r="B74" t="n">
-        <v>794.373621900074</v>
+        <v>794.3736219000764</v>
       </c>
       <c r="C74" t="n">
         <v>0</v>
@@ -6329,7 +6329,7 @@
         <v>0</v>
       </c>
       <c r="E74" t="n">
-        <v>576.8897916428499</v>
+        <v>576.8897916428517</v>
       </c>
       <c r="F74" t="n">
         <v>0</v>
@@ -6338,7 +6338,7 @@
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>217.4838302572241</v>
+        <v>217.4838302572247</v>
       </c>
       <c r="I74" t="n">
         <v>0</v>
@@ -6356,10 +6356,10 @@
         <v>6000</v>
       </c>
       <c r="N74" t="n">
-        <v>762.4062083571499</v>
+        <v>762.4062083571481</v>
       </c>
       <c r="O74" t="n">
-        <v>17.46435020861642</v>
+        <v>17.46435020861637</v>
       </c>
       <c r="P74" t="n">
         <v>278.79</v>
@@ -6433,7 +6433,7 @@
         <v>2400</v>
       </c>
       <c r="M75" t="n">
-        <v>6000</v>
+        <v>5999.999999999999</v>
       </c>
       <c r="N75" t="n">
         <v>1340.7408</v>
@@ -6720,7 +6720,7 @@
         <v>77</v>
       </c>
       <c r="B79" t="n">
-        <v>752.1163110394165</v>
+        <v>826.1136248586828</v>
       </c>
       <c r="C79" t="n">
         <v>0</v>
@@ -6729,7 +6729,7 @@
         <v>0</v>
       </c>
       <c r="E79" t="n">
-        <v>545.2036340709936</v>
+        <v>600.6896670867465</v>
       </c>
       <c r="F79" t="n">
         <v>0</v>
@@ -6738,7 +6738,7 @@
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>206.9126769684229</v>
+        <v>225.4239577719364</v>
       </c>
       <c r="I79" t="n">
         <v>0</v>
@@ -6756,10 +6756,10 @@
         <v>6000</v>
       </c>
       <c r="N79" t="n">
-        <v>819.2419659290064</v>
+        <v>763.7559329132536</v>
       </c>
       <c r="O79" t="n">
-        <v>18.47115643828434</v>
+        <v>17.22013263994709</v>
       </c>
       <c r="P79" t="n">
         <v>278.17</v>
@@ -6880,7 +6880,7 @@
         <v>79</v>
       </c>
       <c r="B81" t="n">
-        <v>749.5157406114762</v>
+        <v>749.5157406114781</v>
       </c>
       <c r="C81" t="n">
         <v>0</v>
@@ -6889,7 +6889,7 @@
         <v>0</v>
       </c>
       <c r="E81" t="n">
-        <v>562.0157406114762</v>
+        <v>562.0157406114777</v>
       </c>
       <c r="F81" t="n">
         <v>0</v>
@@ -6898,7 +6898,7 @@
         <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>187.5</v>
+        <v>187.5000000000005</v>
       </c>
       <c r="I81" t="n">
         <v>0</v>
@@ -6916,10 +6916,10 @@
         <v>6000</v>
       </c>
       <c r="N81" t="n">
-        <v>915.6534593885239</v>
+        <v>915.6534593885224</v>
       </c>
       <c r="O81" t="n">
-        <v>20.58746992807452</v>
+        <v>20.58746992807449</v>
       </c>
       <c r="P81" t="n">
         <v>278.06</v>
@@ -6960,7 +6960,7 @@
         <v>80</v>
       </c>
       <c r="B82" t="n">
-        <v>0</v>
+        <v>-5.623864908597788e-12</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
@@ -6969,7 +6969,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>-4.216990291792789e-12</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -6978,7 +6978,7 @@
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>0</v>
+        <v>-1.406874616804998e-12</v>
       </c>
       <c r="I82" t="n">
         <v>0</v>
@@ -6996,10 +6996,10 @@
         <v>6000</v>
       </c>
       <c r="N82" t="n">
-        <v>1515.4104</v>
+        <v>1515.410400000004</v>
       </c>
       <c r="O82" t="n">
-        <v>34.03791223292248</v>
+        <v>34.03791223292258</v>
       </c>
       <c r="P82" t="n">
         <v>278.02</v>
@@ -7040,7 +7040,7 @@
         <v>81</v>
       </c>
       <c r="B83" t="n">
-        <v>674.5157406114776</v>
+        <v>674.5157406114762</v>
       </c>
       <c r="C83" t="n">
         <v>0</v>
@@ -7049,7 +7049,7 @@
         <v>0</v>
       </c>
       <c r="E83" t="n">
-        <v>487.0157406114772</v>
+        <v>487.0157406114762</v>
       </c>
       <c r="F83" t="n">
         <v>0</v>
@@ -7058,7 +7058,7 @@
         <v>0</v>
       </c>
       <c r="H83" t="n">
-        <v>187.5000000000003</v>
+        <v>187.5</v>
       </c>
       <c r="I83" t="n">
         <v>0</v>
@@ -7076,10 +7076,10 @@
         <v>6000</v>
       </c>
       <c r="N83" t="n">
-        <v>1123.146659388523</v>
+        <v>1123.146659388524</v>
       </c>
       <c r="O83" t="n">
-        <v>25.33604013960124</v>
+        <v>25.33604013960127</v>
       </c>
       <c r="P83" t="n">
         <v>278.19</v>
@@ -7120,7 +7120,7 @@
         <v>82</v>
       </c>
       <c r="B84" t="n">
-        <v>749.5157406114762</v>
+        <v>829.5521743424324</v>
       </c>
       <c r="C84" t="n">
         <v>0</v>
@@ -7129,7 +7129,7 @@
         <v>0</v>
       </c>
       <c r="E84" t="n">
-        <v>562.0157406114762</v>
+        <v>622.0301380976548</v>
       </c>
       <c r="F84" t="n">
         <v>0</v>
@@ -7138,7 +7138,7 @@
         <v>0</v>
       </c>
       <c r="H84" t="n">
-        <v>187.5</v>
+        <v>207.5220362447776</v>
       </c>
       <c r="I84" t="n">
         <v>0</v>
@@ -7156,10 +7156,10 @@
         <v>6000</v>
       </c>
       <c r="N84" t="n">
-        <v>1100.596259388524</v>
+        <v>1040.581861902345</v>
       </c>
       <c r="O84" t="n">
-        <v>25.01781575015112</v>
+        <v>23.6536196374915</v>
       </c>
       <c r="P84" t="n">
         <v>278.49</v>
@@ -7200,7 +7200,7 @@
         <v>83</v>
       </c>
       <c r="B85" t="n">
-        <v>749.5157406114762</v>
+        <v>0</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
@@ -7209,7 +7209,7 @@
         <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>562.0157406114762</v>
+        <v>0</v>
       </c>
       <c r="F85" t="n">
         <v>0</v>
@@ -7218,7 +7218,7 @@
         <v>0</v>
       </c>
       <c r="H85" t="n">
-        <v>187.5</v>
+        <v>0</v>
       </c>
       <c r="I85" t="n">
         <v>0</v>
@@ -7236,10 +7236,10 @@
         <v>6000</v>
       </c>
       <c r="N85" t="n">
-        <v>957.7542593885238</v>
+        <v>1519.77</v>
       </c>
       <c r="O85" t="n">
-        <v>21.87714951634122</v>
+        <v>34.71478742540614</v>
       </c>
       <c r="P85" t="n">
         <v>278.6799999999999</v>
@@ -7280,7 +7280,7 @@
         <v>84</v>
       </c>
       <c r="B86" t="n">
-        <v>749.5157406114762</v>
+        <v>1091.958964238324</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
@@ -7289,7 +7289,7 @@
         <v>0</v>
       </c>
       <c r="E86" t="n">
-        <v>562.0157406114762</v>
+        <v>800.0307311952413</v>
       </c>
       <c r="F86" t="n">
         <v>0</v>
@@ -7298,7 +7298,7 @@
         <v>0</v>
       </c>
       <c r="H86" t="n">
-        <v>187.5</v>
+        <v>291.9282330430827</v>
       </c>
       <c r="I86" t="n">
         <v>0</v>
@@ -7316,10 +7316,10 @@
         <v>6000</v>
       </c>
       <c r="N86" t="n">
-        <v>991.2114593885236</v>
+        <v>753.1964688047585</v>
       </c>
       <c r="O86" t="n">
-        <v>22.78777997329784</v>
+        <v>17.31585651600111</v>
       </c>
       <c r="P86" t="n">
         <v>278.9299999999999</v>
@@ -7360,7 +7360,7 @@
         <v>85</v>
       </c>
       <c r="B87" t="n">
-        <v>0</v>
+        <v>749.5157406114762</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
@@ -7369,7 +7369,7 @@
         <v>0</v>
       </c>
       <c r="E87" t="n">
-        <v>0</v>
+        <v>562.0157406114762</v>
       </c>
       <c r="F87" t="n">
         <v>0</v>
@@ -7378,7 +7378,7 @@
         <v>0</v>
       </c>
       <c r="H87" t="n">
-        <v>0</v>
+        <v>187.5</v>
       </c>
       <c r="I87" t="n">
         <v>0</v>
@@ -7396,10 +7396,10 @@
         <v>6000</v>
       </c>
       <c r="N87" t="n">
-        <v>1549.8084</v>
+        <v>987.7926593885237</v>
       </c>
       <c r="O87" t="n">
-        <v>35.6206142442612</v>
+        <v>22.70331046946932</v>
       </c>
       <c r="P87" t="n">
         <v>278.92</v>
@@ -7440,7 +7440,7 @@
         <v>86</v>
       </c>
       <c r="B88" t="n">
-        <v>799.8802587031403</v>
+        <v>0</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
@@ -7449,7 +7449,7 @@
         <v>0</v>
       </c>
       <c r="E88" t="n">
-        <v>581.018879790657</v>
+        <v>0</v>
       </c>
       <c r="F88" t="n">
         <v>0</v>
@@ -7458,7 +7458,7 @@
         <v>0</v>
       </c>
       <c r="H88" t="n">
-        <v>218.8613789124832</v>
+        <v>0</v>
       </c>
       <c r="I88" t="n">
         <v>0</v>
@@ -7476,10 +7476,10 @@
         <v>6000</v>
       </c>
       <c r="N88" t="n">
-        <v>981.1459202093428</v>
+        <v>1562.1648</v>
       </c>
       <c r="O88" t="n">
-        <v>22.69726262701619</v>
+        <v>36.13821756983399</v>
       </c>
       <c r="P88" t="n">
         <v>279.17</v>
@@ -7840,7 +7840,7 @@
         <v>91</v>
       </c>
       <c r="B93" t="n">
-        <v>674.5157406114757</v>
+        <v>977.9190281375501</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
@@ -7849,7 +7849,7 @@
         <v>0</v>
       </c>
       <c r="E93" t="n">
-        <v>487.0157406114758</v>
+        <v>714.5191993164397</v>
       </c>
       <c r="F93" t="n">
         <v>0</v>
@@ -7858,7 +7858,7 @@
         <v>0</v>
       </c>
       <c r="H93" t="n">
-        <v>187.4999999999999</v>
+        <v>263.3998288211104</v>
       </c>
       <c r="I93" t="n">
         <v>0</v>
@@ -7876,10 +7876,10 @@
         <v>6000</v>
       </c>
       <c r="N93" t="n">
-        <v>994.7610593885242</v>
+        <v>767.2576006835604</v>
       </c>
       <c r="O93" t="n">
-        <v>22.41715063410759</v>
+        <v>17.29031212808023</v>
       </c>
       <c r="P93" t="n">
         <v>278.15</v>
@@ -8000,7 +8000,7 @@
         <v>93</v>
       </c>
       <c r="B95" t="n">
-        <v>1299.254861119656</v>
+        <v>1299.254861119658</v>
       </c>
       <c r="C95" t="n">
         <v>0</v>
@@ -8009,7 +8009,7 @@
         <v>0</v>
       </c>
       <c r="E95" t="n">
-        <v>955.4691705753605</v>
+        <v>955.4691705753622</v>
       </c>
       <c r="F95" t="n">
         <v>0</v>
@@ -8018,7 +8018,7 @@
         <v>0</v>
       </c>
       <c r="H95" t="n">
-        <v>343.7856905442956</v>
+        <v>343.7856905442962</v>
       </c>
       <c r="I95" t="n">
         <v>0</v>
@@ -8027,19 +8027,19 @@
         <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>3000</v>
+        <v>2999.999999999998</v>
       </c>
       <c r="L95" t="n">
-        <v>2400</v>
+        <v>2399.999999999998</v>
       </c>
       <c r="M95" t="n">
-        <v>6000</v>
+        <v>5999.999999999995</v>
       </c>
       <c r="N95" t="n">
-        <v>420.8540294246393</v>
+        <v>420.8540294246376</v>
       </c>
       <c r="O95" t="n">
-        <v>9.384113482906274</v>
+        <v>9.384113482906237</v>
       </c>
       <c r="P95" t="n">
         <v>277.73</v>
@@ -8240,7 +8240,7 @@
         <v>96</v>
       </c>
       <c r="B98" t="n">
-        <v>903.9638853370489</v>
+        <v>903.9638853370484</v>
       </c>
       <c r="C98" t="n">
         <v>0</v>
@@ -8249,7 +8249,7 @@
         <v>0</v>
       </c>
       <c r="E98" t="n">
-        <v>659.184448174206</v>
+        <v>659.1844481742056</v>
       </c>
       <c r="F98" t="n">
         <v>0</v>
@@ -8258,7 +8258,7 @@
         <v>0</v>
       </c>
       <c r="H98" t="n">
-        <v>244.779437162843</v>
+        <v>244.7794371628428</v>
       </c>
       <c r="I98" t="n">
         <v>0</v>
@@ -8276,7 +8276,7 @@
         <v>6000</v>
       </c>
       <c r="N98" t="n">
-        <v>658.0699518257941</v>
+        <v>658.0699518257944</v>
       </c>
       <c r="O98" t="n">
         <v>14.53134123107553</v>
@@ -8578,7 +8578,7 @@
         <v>0</v>
       </c>
       <c r="H102" t="n">
-        <v>187.4999999999996</v>
+        <v>187.4999999999997</v>
       </c>
       <c r="I102" t="n">
         <v>0</v>
@@ -8720,7 +8720,7 @@
         <v>102</v>
       </c>
       <c r="B104" t="n">
-        <v>804.1215219563755</v>
+        <v>804.1215219563759</v>
       </c>
       <c r="C104" t="n">
         <v>0</v>
@@ -8729,7 +8729,7 @@
         <v>0</v>
       </c>
       <c r="E104" t="n">
-        <v>603.0595456126389</v>
+        <v>603.0595456126391</v>
       </c>
       <c r="F104" t="n">
         <v>0</v>
@@ -8756,10 +8756,10 @@
         <v>6000</v>
       </c>
       <c r="N104" t="n">
-        <v>819.270454387361</v>
+        <v>819.2704543873608</v>
       </c>
       <c r="O104" t="n">
-        <v>17.9394105244256</v>
+        <v>17.93941052442559</v>
       </c>
       <c r="P104" t="n">
         <v>277</v>
@@ -8800,7 +8800,7 @@
         <v>103</v>
       </c>
       <c r="B105" t="n">
-        <v>847.2646275294469</v>
+        <v>847.2646275294481</v>
       </c>
       <c r="C105" t="n">
         <v>0</v>
@@ -8809,7 +8809,7 @@
         <v>0</v>
       </c>
       <c r="E105" t="n">
-        <v>635.4151795968093</v>
+        <v>635.4151795968102</v>
       </c>
       <c r="F105" t="n">
         <v>0</v>
@@ -8818,7 +8818,7 @@
         <v>0</v>
       </c>
       <c r="H105" t="n">
-        <v>211.8494479326376</v>
+        <v>211.849447932638</v>
       </c>
       <c r="I105" t="n">
         <v>0</v>
@@ -8836,10 +8836,10 @@
         <v>6000</v>
       </c>
       <c r="N105" t="n">
-        <v>837.0124204031907</v>
+        <v>837.0124204031898</v>
       </c>
       <c r="O105" t="n">
-        <v>18.29185500922098</v>
+        <v>18.29185500922096</v>
       </c>
       <c r="P105" t="n">
         <v>276.92</v>
@@ -8880,7 +8880,7 @@
         <v>104</v>
       </c>
       <c r="B106" t="n">
-        <v>749.882141360526</v>
+        <v>749.8821413605247</v>
       </c>
       <c r="C106" t="n">
         <v>0</v>
@@ -8889,7 +8889,7 @@
         <v>0</v>
       </c>
       <c r="E106" t="n">
-        <v>562.3821413605257</v>
+        <v>562.3821413605247</v>
       </c>
       <c r="F106" t="n">
         <v>0</v>
@@ -8898,7 +8898,7 @@
         <v>0</v>
       </c>
       <c r="H106" t="n">
-        <v>187.5000000000003</v>
+        <v>187.5</v>
       </c>
       <c r="I106" t="n">
         <v>0</v>
@@ -8916,10 +8916,10 @@
         <v>6000</v>
       </c>
       <c r="N106" t="n">
-        <v>955.2542586394742</v>
+        <v>955.2542586394752</v>
       </c>
       <c r="O106" t="n">
-        <v>20.90672193558884</v>
+        <v>20.90672193558887</v>
       </c>
       <c r="P106" t="n">
         <v>276.98</v>
@@ -8960,7 +8960,7 @@
         <v>105</v>
       </c>
       <c r="B107" t="n">
-        <v>0</v>
+        <v>749.8821413605247</v>
       </c>
       <c r="C107" t="n">
         <v>0</v>
@@ -8969,7 +8969,7 @@
         <v>0</v>
       </c>
       <c r="E107" t="n">
-        <v>0</v>
+        <v>562.3821413605247</v>
       </c>
       <c r="F107" t="n">
         <v>0</v>
@@ -8978,7 +8978,7 @@
         <v>0</v>
       </c>
       <c r="H107" t="n">
-        <v>0</v>
+        <v>187.5</v>
       </c>
       <c r="I107" t="n">
         <v>0</v>
@@ -8996,10 +8996,10 @@
         <v>6000</v>
       </c>
       <c r="N107" t="n">
-        <v>1490.118</v>
+        <v>927.7358586394753</v>
       </c>
       <c r="O107" t="n">
-        <v>32.66907097835021</v>
+        <v>20.33950909595998</v>
       </c>
       <c r="P107" t="n">
         <v>277.05</v>
@@ -9040,7 +9040,7 @@
         <v>106</v>
       </c>
       <c r="B108" t="n">
-        <v>674.8821413605247</v>
+        <v>0</v>
       </c>
       <c r="C108" t="n">
         <v>0</v>
@@ -9049,7 +9049,7 @@
         <v>0</v>
       </c>
       <c r="E108" t="n">
-        <v>487.3821413605247</v>
+        <v>0</v>
       </c>
       <c r="F108" t="n">
         <v>0</v>
@@ -9058,7 +9058,7 @@
         <v>0</v>
       </c>
       <c r="H108" t="n">
-        <v>187.5</v>
+        <v>0</v>
       </c>
       <c r="I108" t="n">
         <v>0</v>
@@ -9076,10 +9076,10 @@
         <v>6000</v>
       </c>
       <c r="N108" t="n">
-        <v>1912.617858639475</v>
+        <v>2400</v>
       </c>
       <c r="O108" t="n">
-        <v>42.33914294561502</v>
+        <v>53.12819945211547</v>
       </c>
       <c r="P108" t="n">
         <v>277.44</v>
@@ -9120,7 +9120,7 @@
         <v>107</v>
       </c>
       <c r="B109" t="n">
-        <v>749.8821413605247</v>
+        <v>674.8821413605247</v>
       </c>
       <c r="C109" t="n">
         <v>0</v>
@@ -9129,7 +9129,7 @@
         <v>0</v>
       </c>
       <c r="E109" t="n">
-        <v>562.3821413605247</v>
+        <v>487.3821413605247</v>
       </c>
       <c r="F109" t="n">
         <v>0</v>
@@ -9156,10 +9156,10 @@
         <v>6000</v>
       </c>
       <c r="N109" t="n">
-        <v>1015.515858639475</v>
+        <v>1090.515858639475</v>
       </c>
       <c r="O109" t="n">
-        <v>22.81545402470175</v>
+        <v>24.50046862816165</v>
       </c>
       <c r="P109" t="n">
         <v>278.03</v>
@@ -9440,7 +9440,7 @@
         <v>111</v>
       </c>
       <c r="B113" t="n">
-        <v>892.9601180155264</v>
+        <v>892.960118015525</v>
       </c>
       <c r="C113" t="n">
         <v>0</v>
@@ -9449,7 +9449,7 @@
         <v>0</v>
       </c>
       <c r="E113" t="n">
-        <v>669.6850019764381</v>
+        <v>669.6850019764371</v>
       </c>
       <c r="F113" t="n">
         <v>0</v>
@@ -9458,7 +9458,7 @@
         <v>0</v>
       </c>
       <c r="H113" t="n">
-        <v>223.2751160390883</v>
+        <v>223.275116039088</v>
       </c>
       <c r="I113" t="n">
         <v>0</v>
@@ -9476,10 +9476,10 @@
         <v>6000</v>
       </c>
       <c r="N113" t="n">
-        <v>955.0177980235617</v>
+        <v>955.0177980235627</v>
       </c>
       <c r="O113" t="n">
-        <v>21.63672052388347</v>
+        <v>21.63672052388349</v>
       </c>
       <c r="P113" t="n">
         <v>278.36</v>
@@ -9600,7 +9600,7 @@
         <v>113</v>
       </c>
       <c r="B115" t="n">
-        <v>878.8794856841762</v>
+        <v>878.8794856841756</v>
       </c>
       <c r="C115" t="n">
         <v>0</v>
@@ -9609,7 +9609,7 @@
         <v>0</v>
       </c>
       <c r="E115" t="n">
-        <v>640.3721340605092</v>
+        <v>640.3721340605088</v>
       </c>
       <c r="F115" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
         <v>0</v>
       </c>
       <c r="H115" t="n">
-        <v>238.507351623667</v>
+        <v>238.5073516236669</v>
       </c>
       <c r="I115" t="n">
         <v>0</v>
@@ -9636,10 +9636,10 @@
         <v>6000</v>
       </c>
       <c r="N115" t="n">
-        <v>905.6478659394908</v>
+        <v>905.6478659394912</v>
       </c>
       <c r="O115" t="n">
-        <v>20.41931945075228</v>
+        <v>20.41931945075229</v>
       </c>
       <c r="P115" t="n">
         <v>278.17</v>
@@ -9760,7 +9760,7 @@
         <v>115</v>
       </c>
       <c r="B117" t="n">
-        <v>674.8821413605247</v>
+        <v>674.8821413605264</v>
       </c>
       <c r="C117" t="n">
         <v>0</v>
@@ -9769,7 +9769,7 @@
         <v>0</v>
       </c>
       <c r="E117" t="n">
-        <v>487.3821413605247</v>
+        <v>487.3821413605259</v>
       </c>
       <c r="F117" t="n">
         <v>0</v>
@@ -9778,7 +9778,7 @@
         <v>0</v>
       </c>
       <c r="H117" t="n">
-        <v>187.5</v>
+        <v>187.5000000000004</v>
       </c>
       <c r="I117" t="n">
         <v>0</v>
@@ -9796,10 +9796,10 @@
         <v>6000</v>
       </c>
       <c r="N117" t="n">
-        <v>964.6838586394754</v>
+        <v>964.6838586394741</v>
       </c>
       <c r="O117" t="n">
-        <v>21.73384457212483</v>
+        <v>21.7338445721248</v>
       </c>
       <c r="P117" t="n">
         <v>278.14</v>
@@ -9840,7 +9840,7 @@
         <v>116</v>
       </c>
       <c r="B118" t="n">
-        <v>-3.374102790271704e-13</v>
+        <v>-1.250358696622815e-12</v>
       </c>
       <c r="C118" t="n">
         <v>0</v>
@@ -9849,7 +9849,7 @@
         <v>0</v>
       </c>
       <c r="E118" t="n">
-        <v>0</v>
+        <v>-9.377198928883705e-13</v>
       </c>
       <c r="F118" t="n">
         <v>0</v>
@@ -9858,7 +9858,7 @@
         <v>0</v>
       </c>
       <c r="H118" t="n">
-        <v>-3.374102790271704e-13</v>
+        <v>-3.126388037344441e-13</v>
       </c>
       <c r="I118" t="n">
         <v>0</v>
@@ -9876,10 +9876,10 @@
         <v>6000</v>
       </c>
       <c r="N118" t="n">
-        <v>1404.5724</v>
+        <v>1404.572400000001</v>
       </c>
       <c r="O118" t="n">
-        <v>31.5006004877912</v>
+        <v>31.50060048779122</v>
       </c>
       <c r="P118" t="n">
         <v>277.96</v>
@@ -9920,7 +9920,7 @@
         <v>117</v>
       </c>
       <c r="B119" t="n">
-        <v>1184.624646729123</v>
+        <v>1206.448664344808</v>
       </c>
       <c r="C119" t="n">
         <v>0</v>
@@ -9929,7 +9929,7 @@
         <v>0</v>
       </c>
       <c r="E119" t="n">
-        <v>869.6689913867976</v>
+        <v>886.0361470807986</v>
       </c>
       <c r="F119" t="n">
         <v>0</v>
@@ -9938,7 +9938,7 @@
         <v>0</v>
       </c>
       <c r="H119" t="n">
-        <v>314.9556553423258</v>
+        <v>320.4125172640095</v>
       </c>
       <c r="I119" t="n">
         <v>0</v>
@@ -9956,10 +9956,10 @@
         <v>6000</v>
       </c>
       <c r="N119" t="n">
-        <v>511.4086086132022</v>
+        <v>495.0414529192012</v>
       </c>
       <c r="O119" t="n">
-        <v>11.33786578607626</v>
+        <v>10.97500796273691</v>
       </c>
       <c r="P119" t="n">
         <v>277.5</v>
@@ -10160,7 +10160,7 @@
         <v>120</v>
       </c>
       <c r="B122" t="n">
-        <v>663.2801780127706</v>
+        <v>688.5220984488454</v>
       </c>
       <c r="C122" t="n">
         <v>0</v>
@@ -10169,7 +10169,7 @@
         <v>0</v>
       </c>
       <c r="E122" t="n">
-        <v>475.7801780127706</v>
+        <v>494.611442680593</v>
       </c>
       <c r="F122" t="n">
         <v>0</v>
@@ -10178,7 +10178,7 @@
         <v>0</v>
       </c>
       <c r="H122" t="n">
-        <v>187.5</v>
+        <v>193.9106557682525</v>
       </c>
       <c r="I122" t="n">
         <v>0</v>
@@ -10196,10 +10196,10 @@
         <v>6000</v>
       </c>
       <c r="N122" t="n">
-        <v>863.2050219872292</v>
+        <v>844.3737573194069</v>
       </c>
       <c r="O122" t="n">
-        <v>19.02799563512023</v>
+        <v>18.61289005443419</v>
       </c>
       <c r="P122" t="n">
         <v>277.27</v>
@@ -10347,13 +10347,13 @@
         <v>0</v>
       </c>
       <c r="K124" t="n">
-        <v>3000</v>
+        <v>2999.999999999997</v>
       </c>
       <c r="L124" t="n">
-        <v>2400</v>
+        <v>2399.999999999998</v>
       </c>
       <c r="M124" t="n">
-        <v>6000</v>
+        <v>5999.999999999994</v>
       </c>
       <c r="N124" t="n">
         <v>1312.4832</v>
@@ -10480,7 +10480,7 @@
         <v>124</v>
       </c>
       <c r="B126" t="n">
-        <v>738.2801780127706</v>
+        <v>-7.162260376816952e-12</v>
       </c>
       <c r="C126" t="n">
         <v>0</v>
@@ -10489,7 +10489,7 @@
         <v>0</v>
       </c>
       <c r="E126" t="n">
-        <v>550.7801780127706</v>
+        <v>-5.343270973271095e-12</v>
       </c>
       <c r="F126" t="n">
         <v>0</v>
@@ -10498,7 +10498,7 @@
         <v>0</v>
       </c>
       <c r="H126" t="n">
-        <v>187.5</v>
+        <v>-1.818989403545856e-12</v>
       </c>
       <c r="I126" t="n">
         <v>0</v>
@@ -10507,19 +10507,19 @@
         <v>0</v>
       </c>
       <c r="K126" t="n">
-        <v>3000</v>
+        <v>3000.000000000004</v>
       </c>
       <c r="L126" t="n">
-        <v>2400</v>
+        <v>2400.000000000003</v>
       </c>
       <c r="M126" t="n">
-        <v>6000</v>
+        <v>6000.000000000008</v>
       </c>
       <c r="N126" t="n">
-        <v>731.337021987229</v>
+        <v>1282.117200000005</v>
       </c>
       <c r="O126" t="n">
-        <v>16.07334114257646</v>
+        <v>28.17840000000011</v>
       </c>
       <c r="P126" t="n">
         <v>277.15</v>
@@ -10560,7 +10560,7 @@
         <v>125</v>
       </c>
       <c r="B127" t="n">
-        <v>9.094947017729282e-13</v>
+        <v>663.2801780127706</v>
       </c>
       <c r="C127" t="n">
         <v>0</v>
@@ -10569,7 +10569,7 @@
         <v>0</v>
       </c>
       <c r="E127" t="n">
-        <v>9.094947017729282e-13</v>
+        <v>475.7801780127706</v>
       </c>
       <c r="F127" t="n">
         <v>0</v>
@@ -10578,7 +10578,7 @@
         <v>0</v>
       </c>
       <c r="H127" t="n">
-        <v>0</v>
+        <v>187.5</v>
       </c>
       <c r="I127" t="n">
         <v>0</v>
@@ -10596,10 +10596,10 @@
         <v>6000</v>
       </c>
       <c r="N127" t="n">
-        <v>1297.623599999999</v>
+        <v>821.8434219872292</v>
       </c>
       <c r="O127" t="n">
-        <v>28.49806132813572</v>
+        <v>18.04910471874664</v>
       </c>
       <c r="P127" t="n">
         <v>277.12</v>
@@ -10640,7 +10640,7 @@
         <v>126</v>
       </c>
       <c r="B128" t="n">
-        <v>710.3461160645396</v>
+        <v>738.2801780127706</v>
       </c>
       <c r="C128" t="n">
         <v>0</v>
@@ -10649,7 +10649,7 @@
         <v>0</v>
       </c>
       <c r="E128" t="n">
-        <v>510.8928445999575</v>
+        <v>550.7801780127706</v>
       </c>
       <c r="F128" t="n">
         <v>0</v>
@@ -10658,7 +10658,7 @@
         <v>0</v>
       </c>
       <c r="H128" t="n">
-        <v>199.4532714645822</v>
+        <v>187.5</v>
       </c>
       <c r="I128" t="n">
         <v>0</v>
@@ -10676,10 +10676,10 @@
         <v>6000</v>
       </c>
       <c r="N128" t="n">
-        <v>781.3043554000426</v>
+        <v>741.4170219872294</v>
       </c>
       <c r="O128" t="n">
-        <v>17.15879661569809</v>
+        <v>16.28280170175375</v>
       </c>
       <c r="P128" t="n">
         <v>277.12</v>
@@ -10720,7 +10720,7 @@
         <v>127</v>
       </c>
       <c r="B129" t="n">
-        <v>738.2801780127706</v>
+        <v>738.2801780127875</v>
       </c>
       <c r="C129" t="n">
         <v>0</v>
@@ -10729,7 +10729,7 @@
         <v>0</v>
       </c>
       <c r="E129" t="n">
-        <v>550.7801780127706</v>
+        <v>550.7801780127832</v>
       </c>
       <c r="F129" t="n">
         <v>0</v>
@@ -10738,7 +10738,7 @@
         <v>0</v>
       </c>
       <c r="H129" t="n">
-        <v>187.5</v>
+        <v>187.5000000000043</v>
       </c>
       <c r="I129" t="n">
         <v>0</v>
@@ -10756,10 +10756,10 @@
         <v>6000</v>
       </c>
       <c r="N129" t="n">
-        <v>767.1798219872294</v>
+        <v>767.1798219872169</v>
       </c>
       <c r="O129" t="n">
-        <v>16.81950829240294</v>
+        <v>16.81950829240266</v>
       </c>
       <c r="P129" t="n">
         <v>277.05</v>
@@ -11280,7 +11280,7 @@
         <v>134</v>
       </c>
       <c r="B136" t="n">
-        <v>908.8157774552147</v>
+        <v>908.8157774552143</v>
       </c>
       <c r="C136" t="n">
         <v>0</v>
@@ -11289,7 +11289,7 @@
         <v>0</v>
       </c>
       <c r="E136" t="n">
-        <v>658.9574394332208</v>
+        <v>658.9574394332204</v>
       </c>
       <c r="F136" t="n">
         <v>0</v>
@@ -11298,7 +11298,7 @@
         <v>0</v>
       </c>
       <c r="H136" t="n">
-        <v>249.858338021994</v>
+        <v>249.8583380219939</v>
       </c>
       <c r="I136" t="n">
         <v>0</v>
@@ -11316,10 +11316,10 @@
         <v>6000</v>
       </c>
       <c r="N136" t="n">
-        <v>674.3997605667792</v>
+        <v>674.3997605667795</v>
       </c>
       <c r="O136" t="n">
-        <v>15.16697988455593</v>
+        <v>15.16697988455594</v>
       </c>
       <c r="P136" t="n">
         <v>278.07</v>
@@ -11520,7 +11520,7 @@
         <v>137</v>
       </c>
       <c r="B139" t="n">
-        <v>663.2801780127706</v>
+        <v>663.2801780127648</v>
       </c>
       <c r="C139" t="n">
         <v>0</v>
@@ -11529,7 +11529,7 @@
         <v>0</v>
       </c>
       <c r="E139" t="n">
-        <v>475.7801780127706</v>
+        <v>475.7801780127663</v>
       </c>
       <c r="F139" t="n">
         <v>0</v>
@@ -11538,7 +11538,7 @@
         <v>0</v>
       </c>
       <c r="H139" t="n">
-        <v>187.5</v>
+        <v>187.4999999999985</v>
       </c>
       <c r="I139" t="n">
         <v>0</v>
@@ -11556,10 +11556,10 @@
         <v>6000</v>
       </c>
       <c r="N139" t="n">
-        <v>874.3350219872291</v>
+        <v>874.3350219872334</v>
       </c>
       <c r="O139" t="n">
-        <v>19.01865293354133</v>
+        <v>19.01865293354142</v>
       </c>
       <c r="P139" t="n">
         <v>276.73</v>
@@ -11680,7 +11680,7 @@
         <v>139</v>
       </c>
       <c r="B141" t="n">
-        <v>738.2801780127706</v>
+        <v>738.2801780127725</v>
       </c>
       <c r="C141" t="n">
         <v>0</v>
@@ -11689,7 +11689,7 @@
         <v>0</v>
       </c>
       <c r="E141" t="n">
-        <v>550.7801780127706</v>
+        <v>550.780178012772</v>
       </c>
       <c r="F141" t="n">
         <v>0</v>
@@ -11698,7 +11698,7 @@
         <v>0</v>
       </c>
       <c r="H141" t="n">
-        <v>187.5</v>
+        <v>187.5000000000005</v>
       </c>
       <c r="I141" t="n">
         <v>0</v>
@@ -11716,10 +11716,10 @@
         <v>6000</v>
       </c>
       <c r="N141" t="n">
-        <v>786.9870219872291</v>
+        <v>786.9870219872278</v>
       </c>
       <c r="O141" t="n">
-        <v>16.86686895785313</v>
+        <v>16.8668689578531</v>
       </c>
       <c r="P141" t="n">
         <v>276.12</v>
@@ -11840,7 +11840,7 @@
         <v>141</v>
       </c>
       <c r="B143" t="n">
-        <v>1187.163682357754</v>
+        <v>1187.163682357758</v>
       </c>
       <c r="C143" t="n">
         <v>0</v>
@@ -11849,7 +11849,7 @@
         <v>0</v>
       </c>
       <c r="E143" t="n">
-        <v>866.6137102874143</v>
+        <v>866.6137102874176</v>
       </c>
       <c r="F143" t="n">
         <v>0</v>
@@ -11858,7 +11858,7 @@
         <v>0</v>
       </c>
       <c r="H143" t="n">
-        <v>320.5499720703394</v>
+        <v>320.5499720703405</v>
       </c>
       <c r="I143" t="n">
         <v>0</v>
@@ -11876,10 +11876,10 @@
         <v>6000</v>
       </c>
       <c r="N143" t="n">
-        <v>428.7082897125856</v>
+        <v>428.7082897125823</v>
       </c>
       <c r="O143" t="n">
-        <v>9.109097547742918</v>
+        <v>9.109097547742849</v>
       </c>
       <c r="P143" t="n">
         <v>275.76</v>
@@ -12560,7 +12560,7 @@
         <v>150</v>
       </c>
       <c r="B152" t="n">
-        <v>830.7139884371149</v>
+        <v>840.8406264764045</v>
       </c>
       <c r="C152" t="n">
         <v>0</v>
@@ -12569,7 +12569,7 @@
         <v>0</v>
       </c>
       <c r="E152" t="n">
-        <v>617.4290816197433</v>
+        <v>624.9557164321141</v>
       </c>
       <c r="F152" t="n">
         <v>0</v>
@@ -12578,7 +12578,7 @@
         <v>0</v>
       </c>
       <c r="H152" t="n">
-        <v>213.2849068173716</v>
+        <v>215.8849100442905</v>
       </c>
       <c r="I152" t="n">
         <v>0</v>
@@ -12596,10 +12596,10 @@
         <v>6000</v>
       </c>
       <c r="N152" t="n">
-        <v>668.8881183802564</v>
+        <v>661.3614835678857</v>
       </c>
       <c r="O152" t="n">
-        <v>13.84180901482721</v>
+        <v>13.68605465362034</v>
       </c>
       <c r="P152" t="n">
         <v>274.64</v>
@@ -12640,7 +12640,7 @@
         <v>151</v>
       </c>
       <c r="B153" t="n">
-        <v>1460.570981380599</v>
+        <v>1460.570981380598</v>
       </c>
       <c r="C153" t="n">
         <v>0</v>
@@ -12658,7 +12658,7 @@
         <v>0</v>
       </c>
       <c r="H153" t="n">
-        <v>375</v>
+        <v>374.9999999999998</v>
       </c>
       <c r="I153" t="n">
         <v>0</v>
@@ -12676,10 +12676,10 @@
         <v>6000</v>
       </c>
       <c r="N153" t="n">
-        <v>214.4802186194006</v>
+        <v>214.4802186194011</v>
       </c>
       <c r="O153" t="n">
-        <v>4.443574219079105</v>
+        <v>4.443574219079115</v>
       </c>
       <c r="P153" t="n">
         <v>274.69</v>
@@ -12720,7 +12720,7 @@
         <v>152</v>
       </c>
       <c r="B154" t="n">
-        <v>730.2854906902991</v>
+        <v>836.3385825111396</v>
       </c>
       <c r="C154" t="n">
         <v>0</v>
@@ -12729,7 +12729,7 @@
         <v>0</v>
       </c>
       <c r="E154" t="n">
-        <v>542.7854906902992</v>
+        <v>621.6095673247481</v>
       </c>
       <c r="F154" t="n">
         <v>0</v>
@@ -12738,7 +12738,7 @@
         <v>0</v>
       </c>
       <c r="H154" t="n">
-        <v>187.4999999999999</v>
+        <v>214.7290151863915</v>
       </c>
       <c r="I154" t="n">
         <v>0</v>
@@ -12756,10 +12756,10 @@
         <v>6000</v>
       </c>
       <c r="N154" t="n">
-        <v>739.0797093097008</v>
+        <v>660.2556326752518</v>
       </c>
       <c r="O154" t="n">
-        <v>15.27655455373503</v>
+        <v>13.64728467704117</v>
       </c>
       <c r="P154" t="n">
         <v>274.59</v>
@@ -12800,7 +12800,7 @@
         <v>153</v>
       </c>
       <c r="B155" t="n">
-        <v>730.2854906902995</v>
+        <v>0</v>
       </c>
       <c r="C155" t="n">
         <v>0</v>
@@ -12809,7 +12809,7 @@
         <v>0</v>
       </c>
       <c r="E155" t="n">
-        <v>542.7854906902995</v>
+        <v>0</v>
       </c>
       <c r="F155" t="n">
         <v>0</v>
@@ -12818,7 +12818,7 @@
         <v>0</v>
       </c>
       <c r="H155" t="n">
-        <v>187.5</v>
+        <v>0</v>
       </c>
       <c r="I155" t="n">
         <v>0</v>
@@ -12836,10 +12836,10 @@
         <v>6000</v>
       </c>
       <c r="N155" t="n">
-        <v>738.2145093097005</v>
+        <v>1281</v>
       </c>
       <c r="O155" t="n">
-        <v>15.50016029625891</v>
+        <v>26.89693183905935</v>
       </c>
       <c r="P155" t="n">
         <v>275.26</v>
@@ -12880,7 +12880,7 @@
         <v>154</v>
       </c>
       <c r="B156" t="n">
-        <v>0</v>
+        <v>655.2854906902995</v>
       </c>
       <c r="C156" t="n">
         <v>0</v>
@@ -12889,7 +12889,7 @@
         <v>0</v>
       </c>
       <c r="E156" t="n">
-        <v>0</v>
+        <v>467.7854906902995</v>
       </c>
       <c r="F156" t="n">
         <v>0</v>
@@ -12898,7 +12898,7 @@
         <v>0</v>
       </c>
       <c r="H156" t="n">
-        <v>0</v>
+        <v>187.5</v>
       </c>
       <c r="I156" t="n">
         <v>0</v>
@@ -12916,10 +12916,10 @@
         <v>6000</v>
       </c>
       <c r="N156" t="n">
-        <v>1294.1208</v>
+        <v>826.3353093097004</v>
       </c>
       <c r="O156" t="n">
-        <v>27.45780771780932</v>
+        <v>17.53264149178519</v>
       </c>
       <c r="P156" t="n">
         <v>275.7</v>
@@ -12960,7 +12960,7 @@
         <v>155</v>
       </c>
       <c r="B157" t="n">
-        <v>655.2854906902995</v>
+        <v>869.1593581332944</v>
       </c>
       <c r="C157" t="n">
         <v>0</v>
@@ -12969,7 +12969,7 @@
         <v>0</v>
       </c>
       <c r="E157" t="n">
-        <v>467.7854906902995</v>
+        <v>646.0036447479054</v>
       </c>
       <c r="F157" t="n">
         <v>0</v>
@@ -12978,7 +12978,7 @@
         <v>0</v>
       </c>
       <c r="H157" t="n">
-        <v>187.5</v>
+        <v>223.155713385389</v>
       </c>
       <c r="I157" t="n">
         <v>0</v>
@@ -12996,10 +12996,10 @@
         <v>6000</v>
       </c>
       <c r="N157" t="n">
-        <v>818.9349093097002</v>
+        <v>640.7167552520943</v>
       </c>
       <c r="O157" t="n">
-        <v>17.62382115047506</v>
+        <v>13.78849206977122</v>
       </c>
       <c r="P157" t="n">
         <v>276.29</v>
@@ -13040,7 +13040,7 @@
         <v>156</v>
       </c>
       <c r="B158" t="n">
-        <v>730.2854906902995</v>
+        <v>0</v>
       </c>
       <c r="C158" t="n">
         <v>0</v>
@@ -13049,7 +13049,7 @@
         <v>0</v>
       </c>
       <c r="E158" t="n">
-        <v>542.7854906902995</v>
+        <v>0</v>
       </c>
       <c r="F158" t="n">
         <v>0</v>
@@ -13058,7 +13058,7 @@
         <v>0</v>
       </c>
       <c r="H158" t="n">
-        <v>187.5</v>
+        <v>0</v>
       </c>
       <c r="I158" t="n">
         <v>0</v>
@@ -13076,10 +13076,10 @@
         <v>6000</v>
       </c>
       <c r="N158" t="n">
-        <v>752.4105093097004</v>
+        <v>1295.196</v>
       </c>
       <c r="O158" t="n">
-        <v>16.29873026584064</v>
+        <v>28.05655952993422</v>
       </c>
       <c r="P158" t="n">
         <v>276.56</v>
@@ -13280,7 +13280,7 @@
         <v>159</v>
       </c>
       <c r="B161" t="n">
-        <v>0</v>
+        <v>936.3516714746185</v>
       </c>
       <c r="C161" t="n">
         <v>0</v>
@@ -13289,7 +13289,7 @@
         <v>0</v>
       </c>
       <c r="E161" t="n">
-        <v>0</v>
+        <v>676.6882373534703</v>
       </c>
       <c r="F161" t="n">
         <v>0</v>
@@ -13298,7 +13298,7 @@
         <v>0</v>
       </c>
       <c r="H161" t="n">
-        <v>0</v>
+        <v>259.6634341211482</v>
       </c>
       <c r="I161" t="n">
         <v>0</v>
@@ -13316,10 +13316,10 @@
         <v>6000</v>
       </c>
       <c r="N161" t="n">
-        <v>1288.5852</v>
+        <v>611.8969626465297</v>
       </c>
       <c r="O161" t="n">
-        <v>28.22285933307782</v>
+        <v>13.40189372275157</v>
       </c>
       <c r="P161" t="n">
         <v>277.01</v>
@@ -13440,7 +13440,7 @@
         <v>161</v>
       </c>
       <c r="B163" t="n">
-        <v>655.2854906902995</v>
+        <v>5.383810838882299e-13</v>
       </c>
       <c r="C163" t="n">
         <v>0</v>
@@ -13449,7 +13449,7 @@
         <v>0</v>
       </c>
       <c r="E163" t="n">
-        <v>467.7854906902995</v>
+        <v>0</v>
       </c>
       <c r="F163" t="n">
         <v>0</v>
@@ -13458,7 +13458,7 @@
         <v>0</v>
       </c>
       <c r="H163" t="n">
-        <v>187.5</v>
+        <v>5.383810838882299e-13</v>
       </c>
       <c r="I163" t="n">
         <v>0</v>
@@ -13476,10 +13476,10 @@
         <v>6000</v>
       </c>
       <c r="N163" t="n">
-        <v>825.5289093097002</v>
+        <v>1293.3144</v>
       </c>
       <c r="O163" t="n">
-        <v>17.38687677568872</v>
+        <v>27.23914069081718</v>
       </c>
       <c r="P163" t="n">
         <v>275.39</v>
@@ -13520,7 +13520,7 @@
         <v>162</v>
       </c>
       <c r="B164" t="n">
-        <v>730.2854906902995</v>
+        <v>662.4149293882379</v>
       </c>
       <c r="C164" t="n">
         <v>0</v>
@@ -13529,7 +13529,7 @@
         <v>0</v>
       </c>
       <c r="E164" t="n">
-        <v>542.7854906902995</v>
+        <v>473.0844538099817</v>
       </c>
       <c r="F164" t="n">
         <v>0</v>
@@ -13538,7 +13538,7 @@
         <v>0</v>
       </c>
       <c r="H164" t="n">
-        <v>187.5</v>
+        <v>189.3304755782562</v>
       </c>
       <c r="I164" t="n">
         <v>0</v>
@@ -13556,10 +13556,10 @@
         <v>6000</v>
       </c>
       <c r="N164" t="n">
-        <v>757.6353093097001</v>
+        <v>827.3363461900179</v>
       </c>
       <c r="O164" t="n">
-        <v>15.68927954669082</v>
+        <v>17.13266403375476</v>
       </c>
       <c r="P164" t="n">
         <v>274.67</v>
@@ -13760,7 +13760,7 @@
         <v>165</v>
       </c>
       <c r="B167" t="n">
-        <v>945.9405709287453</v>
+        <v>1207.976844833663</v>
       </c>
       <c r="C167" t="n">
         <v>0</v>
@@ -13769,7 +13769,7 @@
         <v>0</v>
       </c>
       <c r="E167" t="n">
-        <v>703.071365241135</v>
+        <v>897.8301127765632</v>
       </c>
       <c r="F167" t="n">
         <v>0</v>
@@ -13778,7 +13778,7 @@
         <v>0</v>
       </c>
       <c r="H167" t="n">
-        <v>242.8692056876102</v>
+        <v>310.1467320570995</v>
       </c>
       <c r="I167" t="n">
         <v>0</v>
@@ -13796,10 +13796,10 @@
         <v>6000</v>
       </c>
       <c r="N167" t="n">
-        <v>605.438634758865</v>
+        <v>410.6798872234368</v>
       </c>
       <c r="O167" t="n">
-        <v>12.16625826548169</v>
+        <v>8.252591238068607</v>
       </c>
       <c r="P167" t="n">
         <v>273.36</v>
@@ -13996,6 +13996,6 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
 </worksheet>
 </file>
--- a/res_winter_rb.xlsx
+++ b/res_winter_rb.xlsx
@@ -4,7 +4,7 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
@@ -53,18 +53,18 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z169"/>
+  <dimension ref="A1:V169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -534,26 +534,6 @@
           <t>c_el</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -587,13 +567,13 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>2986.570612333543</v>
+        <v>3000.000000000001</v>
       </c>
       <c r="L2" t="n">
-        <v>2389.256489866835</v>
+        <v>2400.000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>5973.141224667086</v>
+        <v>6000.000000000002</v>
       </c>
       <c r="N2" t="n">
         <v>571.3924</v>
@@ -621,18 +601,6 @@
       </c>
       <c r="V2" t="n">
         <v>0.16</v>
-      </c>
-      <c r="W2" t="n">
-        <v>2</v>
-      </c>
-      <c r="X2" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -702,18 +670,6 @@
       <c r="V3" t="n">
         <v>0.16</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -782,18 +738,6 @@
       <c r="V4" t="n">
         <v>0.16</v>
       </c>
-      <c r="W4" t="n">
-        <v>2</v>
-      </c>
-      <c r="X4" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -862,18 +806,6 @@
       <c r="V5" t="n">
         <v>0.16</v>
       </c>
-      <c r="W5" t="n">
-        <v>2</v>
-      </c>
-      <c r="X5" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -942,18 +874,6 @@
       <c r="V6" t="n">
         <v>0.16</v>
       </c>
-      <c r="W6" t="n">
-        <v>2</v>
-      </c>
-      <c r="X6" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
@@ -1022,18 +942,6 @@
       <c r="V7" t="n">
         <v>0.16</v>
       </c>
-      <c r="W7" t="n">
-        <v>2</v>
-      </c>
-      <c r="X7" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -1102,25 +1010,13 @@
       <c r="V8" t="n">
         <v>0.16</v>
       </c>
-      <c r="W8" t="n">
-        <v>2</v>
-      </c>
-      <c r="X8" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>737.9089489947985</v>
+        <v>753.1270348803744</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -1129,7 +1025,7 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>550.4089489947985</v>
+        <v>561.7601741959601</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -1138,7 +1034,7 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>187.5</v>
+        <v>191.3668606844143</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -1156,10 +1052,10 @@
         <v>6000</v>
       </c>
       <c r="N9" t="n">
-        <v>959.1466510052014</v>
+        <v>947.7954258040398</v>
       </c>
       <c r="O9" t="n">
-        <v>21.21653820727094</v>
+        <v>20.96544656979571</v>
       </c>
       <c r="P9" t="n">
         <v>277.41</v>
@@ -1181,18 +1077,6 @@
       </c>
       <c r="V9" t="n">
         <v>0.16</v>
-      </c>
-      <c r="W9" t="n">
-        <v>2</v>
-      </c>
-      <c r="X9" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -1200,7 +1084,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>4.474161863343995e-13</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -1209,7 +1093,7 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>3.337293486127834e-13</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -1218,7 +1102,7 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1.13686837721616e-13</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -1236,7 +1120,7 @@
         <v>6000</v>
       </c>
       <c r="N10" t="n">
-        <v>1531.0176</v>
+        <v>1531.017599999999</v>
       </c>
       <c r="O10" t="n">
         <v>33.90019595903681</v>
@@ -1261,18 +1145,6 @@
       </c>
       <c r="V10" t="n">
         <v>0.25</v>
-      </c>
-      <c r="W10" t="n">
-        <v>2</v>
-      </c>
-      <c r="X10" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1342,25 +1214,13 @@
       <c r="V11" t="n">
         <v>0.25</v>
       </c>
-      <c r="W11" t="n">
-        <v>2</v>
-      </c>
-      <c r="X11" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>737.9089489947985</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
@@ -1369,7 +1229,7 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>550.4089489947985</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -1378,7 +1238,7 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>187.5</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1396,10 +1256,10 @@
         <v>6000</v>
       </c>
       <c r="N12" t="n">
-        <v>1005.439051005201</v>
+        <v>1555.848</v>
       </c>
       <c r="O12" t="n">
-        <v>22.53210938439578</v>
+        <v>34.86689450389375</v>
       </c>
       <c r="P12" t="n">
         <v>277.9299999999999</v>
@@ -1421,18 +1281,6 @@
       </c>
       <c r="V12" t="n">
         <v>0.25</v>
-      </c>
-      <c r="W12" t="n">
-        <v>2</v>
-      </c>
-      <c r="X12" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1440,7 +1288,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>662.9089489947985</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -1449,7 +1297,7 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>475.4089489947985</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -1458,7 +1306,7 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>187.5</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -1476,10 +1324,10 @@
         <v>6000</v>
       </c>
       <c r="N13" t="n">
-        <v>1557.1836</v>
+        <v>1081.774651005201</v>
       </c>
       <c r="O13" t="n">
-        <v>35.01157584103878</v>
+        <v>24.32252384149298</v>
       </c>
       <c r="P13" t="n">
         <v>278.06</v>
@@ -1501,18 +1349,6 @@
       </c>
       <c r="V13" t="n">
         <v>0.25</v>
-      </c>
-      <c r="W13" t="n">
-        <v>2</v>
-      </c>
-      <c r="X13" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1520,7 +1356,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>737.9089489947985</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
@@ -1529,7 +1365,7 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>550.4089489947985</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -1538,7 +1374,7 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>187.5</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -1556,10 +1392,10 @@
         <v>6000</v>
       </c>
       <c r="N14" t="n">
-        <v>1550.5476</v>
+        <v>1000.138651005202</v>
       </c>
       <c r="O14" t="n">
-        <v>35.03072804292574</v>
+        <v>22.59562046891165</v>
       </c>
       <c r="P14" t="n">
         <v>278.25</v>
@@ -1581,18 +1417,6 @@
       </c>
       <c r="V14" t="n">
         <v>0.25</v>
-      </c>
-      <c r="W14" t="n">
-        <v>2</v>
-      </c>
-      <c r="X14" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1600,7 +1424,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>662.9089489947985</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
@@ -1609,7 +1433,7 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>475.4089489947985</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -1618,7 +1442,7 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>187.5</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -1636,10 +1460,10 @@
         <v>6000</v>
       </c>
       <c r="N15" t="n">
-        <v>1080.153451005201</v>
+        <v>1555.5624</v>
       </c>
       <c r="O15" t="n">
-        <v>24.49674729423561</v>
+        <v>35.27852360028348</v>
       </c>
       <c r="P15" t="n">
         <v>278.4</v>
@@ -1661,18 +1485,6 @@
       </c>
       <c r="V15" t="n">
         <v>0.25</v>
-      </c>
-      <c r="W15" t="n">
-        <v>2</v>
-      </c>
-      <c r="X15" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1680,7 +1492,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>737.9089489947985</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
@@ -1689,7 +1501,7 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>550.4089489947985</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -1698,7 +1510,7 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>187.5</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -1716,10 +1528,10 @@
         <v>6000</v>
       </c>
       <c r="N16" t="n">
-        <v>1008.614251005201</v>
+        <v>1559.0232</v>
       </c>
       <c r="O16" t="n">
-        <v>22.87431327580896</v>
+        <v>35.35701091424522</v>
       </c>
       <c r="P16" t="n">
         <v>278.4</v>
@@ -1741,18 +1553,6 @@
       </c>
       <c r="V16" t="n">
         <v>0.25</v>
-      </c>
-      <c r="W16" t="n">
-        <v>2</v>
-      </c>
-      <c r="X16" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1760,7 +1560,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>1122.561121350132</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
@@ -1769,7 +1569,7 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>818.2651637539703</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -1778,7 +1578,7 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>304.2959575961622</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -1796,10 +1596,10 @@
         <v>6000</v>
       </c>
       <c r="N17" t="n">
-        <v>1569.5568</v>
+        <v>751.2916362460295</v>
       </c>
       <c r="O17" t="n">
-        <v>35.50531429379328</v>
+        <v>16.99514517169018</v>
       </c>
       <c r="P17" t="n">
         <v>278.3</v>
@@ -1821,18 +1621,6 @@
       </c>
       <c r="V17" t="n">
         <v>0.25</v>
-      </c>
-      <c r="W17" t="n">
-        <v>2</v>
-      </c>
-      <c r="X17" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1902,25 +1690,13 @@
       <c r="V18" t="n">
         <v>0.25</v>
       </c>
-      <c r="W18" t="n">
-        <v>2</v>
-      </c>
-      <c r="X18" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>662.9089489947985</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -1929,7 +1705,7 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>475.4089489947985</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -1938,7 +1714,7 @@
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>187.5</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -1956,10 +1732,10 @@
         <v>6000</v>
       </c>
       <c r="N19" t="n">
-        <v>1103.900251005201</v>
+        <v>1579.3092</v>
       </c>
       <c r="O19" t="n">
-        <v>24.85142393077895</v>
+        <v>35.55401170643852</v>
       </c>
       <c r="P19" t="n">
         <v>278.11</v>
@@ -1981,18 +1757,6 @@
       </c>
       <c r="V19" t="n">
         <v>0.25</v>
-      </c>
-      <c r="W19" t="n">
-        <v>2</v>
-      </c>
-      <c r="X19" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -2000,7 +1764,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>737.9089489947985</v>
+        <v>745.2729291608771</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
@@ -2009,7 +1773,7 @@
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>550.4089489947985</v>
+        <v>536.8445391444977</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -2018,7 +1782,7 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>187.5</v>
+        <v>208.4283900163794</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -2036,10 +1800,10 @@
         <v>6000</v>
       </c>
       <c r="N20" t="n">
-        <v>1001.289451005201</v>
+        <v>1014.853860855502</v>
       </c>
       <c r="O20" t="n">
-        <v>22.54141042334986</v>
+        <v>22.84677759692709</v>
       </c>
       <c r="P20" t="n">
         <v>278.11</v>
@@ -2061,18 +1825,6 @@
       </c>
       <c r="V20" t="n">
         <v>0.25</v>
-      </c>
-      <c r="W20" t="n">
-        <v>2</v>
-      </c>
-      <c r="X20" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -2142,18 +1894,6 @@
       <c r="V21" t="n">
         <v>0.25</v>
       </c>
-      <c r="W21" t="n">
-        <v>2</v>
-      </c>
-      <c r="X21" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
@@ -2222,25 +1962,13 @@
       <c r="V22" t="n">
         <v>0.25</v>
       </c>
-      <c r="W22" t="n">
-        <v>2</v>
-      </c>
-      <c r="X22" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>662.9089489947985</v>
+        <v>662.9089489947989</v>
       </c>
       <c r="C23" t="n">
         <v>0</v>
@@ -2249,7 +1977,7 @@
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>475.4089489947985</v>
+        <v>475.4089489947989</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -2258,7 +1986,7 @@
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>187.5</v>
+        <v>187.5000000000001</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -2267,19 +1995,19 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>3000</v>
+        <v>3000.000000000001</v>
       </c>
       <c r="L23" t="n">
-        <v>2400</v>
+        <v>2400.000000000001</v>
       </c>
       <c r="M23" t="n">
-        <v>6000</v>
+        <v>6000.000000000002</v>
       </c>
       <c r="N23" t="n">
-        <v>932.6326510052018</v>
+        <v>932.6326510052013</v>
       </c>
       <c r="O23" t="n">
-        <v>20.90050201143372</v>
+        <v>20.90050201143371</v>
       </c>
       <c r="P23" t="n">
         <v>277.9299999999999</v>
@@ -2301,18 +2029,6 @@
       </c>
       <c r="V23" t="n">
         <v>0.16</v>
-      </c>
-      <c r="W23" t="n">
-        <v>2</v>
-      </c>
-      <c r="X23" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -2382,18 +2098,6 @@
       <c r="V24" t="n">
         <v>0.16</v>
       </c>
-      <c r="W24" t="n">
-        <v>2</v>
-      </c>
-      <c r="X24" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
@@ -2462,25 +2166,13 @@
       <c r="V25" t="n">
         <v>0.16</v>
       </c>
-      <c r="W25" t="n">
-        <v>2</v>
-      </c>
-      <c r="X25" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
         <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>784.0466815706947</v>
+        <v>929.3513128961123</v>
       </c>
       <c r="C26" t="n">
         <v>0</v>
@@ -2489,7 +2181,7 @@
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>566.7456994643405</v>
+        <v>675.2946575894578</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -2498,7 +2190,7 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>217.3009821063542</v>
+        <v>254.0566553066545</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -2516,10 +2208,10 @@
         <v>6000</v>
       </c>
       <c r="N26" t="n">
-        <v>826.1255005356593</v>
+        <v>717.5765424105421</v>
       </c>
       <c r="O26" t="n">
-        <v>18.38387761970869</v>
+        <v>15.9683236141428</v>
       </c>
       <c r="P26" t="n">
         <v>277.65</v>
@@ -2541,18 +2233,6 @@
       </c>
       <c r="V26" t="n">
         <v>0.16</v>
-      </c>
-      <c r="W26" t="n">
-        <v>2</v>
-      </c>
-      <c r="X26" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -2622,18 +2302,6 @@
       <c r="V27" t="n">
         <v>0.16</v>
       </c>
-      <c r="W27" t="n">
-        <v>2</v>
-      </c>
-      <c r="X27" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
@@ -2702,25 +2370,13 @@
       <c r="V28" t="n">
         <v>0.16</v>
       </c>
-      <c r="W28" t="n">
-        <v>2</v>
-      </c>
-      <c r="X28" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
         <v>27</v>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>666.2357331899759</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
@@ -2729,7 +2385,7 @@
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>478.7357331899759</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -2738,7 +2394,7 @@
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>187.5</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -2756,10 +2412,10 @@
         <v>6000</v>
       </c>
       <c r="N29" t="n">
-        <v>1384.9164</v>
+        <v>906.1806668100241</v>
       </c>
       <c r="O29" t="n">
-        <v>30.71874899492611</v>
+        <v>20.09993992979786</v>
       </c>
       <c r="P29" t="n">
         <v>277.52</v>
@@ -2781,18 +2437,6 @@
       </c>
       <c r="V29" t="n">
         <v>0.16</v>
-      </c>
-      <c r="W29" t="n">
-        <v>2</v>
-      </c>
-      <c r="X29" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2800,7 +2444,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="n">
-        <v>750.9313694207765</v>
+        <v>0</v>
       </c>
       <c r="C30" t="n">
         <v>0</v>
@@ -2809,7 +2453,7 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>542.0071030474701</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -2818,7 +2462,7 @@
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>208.9242663733064</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -2836,10 +2480,10 @@
         <v>6000</v>
       </c>
       <c r="N30" t="n">
-        <v>831.3760969525297</v>
+        <v>1373.3832</v>
       </c>
       <c r="O30" t="n">
-        <v>18.42690966814494</v>
+        <v>30.44014406826617</v>
       </c>
       <c r="P30" t="n">
         <v>277.49</v>
@@ -2861,18 +2505,6 @@
       </c>
       <c r="V30" t="n">
         <v>0.16</v>
-      </c>
-      <c r="W30" t="n">
-        <v>2</v>
-      </c>
-      <c r="X30" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2880,7 +2512,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="n">
-        <v>-3.19582712600225e-12</v>
+        <v>0</v>
       </c>
       <c r="C31" t="n">
         <v>0</v>
@@ -2889,7 +2521,7 @@
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>-2.387423592153937e-12</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -2898,7 +2530,7 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-8.08403533848313e-13</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
@@ -2916,10 +2548,10 @@
         <v>6000</v>
       </c>
       <c r="N31" t="n">
-        <v>1422.078000000002</v>
+        <v>1422.078</v>
       </c>
       <c r="O31" t="n">
-        <v>31.47234701781568</v>
+        <v>31.47234701781562</v>
       </c>
       <c r="P31" t="n">
         <v>277.4299999999999</v>
@@ -2941,18 +2573,6 @@
       </c>
       <c r="V31" t="n">
         <v>0.16</v>
-      </c>
-      <c r="W31" t="n">
-        <v>2</v>
-      </c>
-      <c r="X31" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -3022,25 +2642,13 @@
       <c r="V32" t="n">
         <v>0.16</v>
       </c>
-      <c r="W32" t="n">
-        <v>2</v>
-      </c>
-      <c r="X32" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
         <v>31</v>
       </c>
       <c r="B33" t="n">
-        <v>666.3394231437037</v>
+        <v>847.975750970432</v>
       </c>
       <c r="C33" t="n">
         <v>0</v>
@@ -3049,7 +2657,7 @@
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>478.8131941514231</v>
+        <v>614.5035294381737</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -3058,7 +2666,7 @@
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>187.5262289922806</v>
+        <v>233.4722215322583</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
@@ -3076,10 +2684,10 @@
         <v>6000</v>
       </c>
       <c r="N33" t="n">
-        <v>1095.170405848577</v>
+        <v>959.4800705618261</v>
       </c>
       <c r="O33" t="n">
-        <v>24.20734188044267</v>
+        <v>21.2080804699655</v>
       </c>
       <c r="P33" t="n">
         <v>277.38</v>
@@ -3101,18 +2709,6 @@
       </c>
       <c r="V33" t="n">
         <v>0.16</v>
-      </c>
-      <c r="W33" t="n">
-        <v>2</v>
-      </c>
-      <c r="X33" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -3120,7 +2716,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="n">
-        <v>741.2357331899756</v>
+        <v>741.235733189976</v>
       </c>
       <c r="C34" t="n">
         <v>0</v>
@@ -3129,7 +2725,7 @@
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>553.7357331899757</v>
+        <v>553.735733189976</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -3138,7 +2734,7 @@
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>187.4999999999999</v>
+        <v>187.5</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
@@ -3159,7 +2755,7 @@
         <v>1019.878266810024</v>
       </c>
       <c r="O34" t="n">
-        <v>22.63880725438454</v>
+        <v>22.63880725438453</v>
       </c>
       <c r="P34" t="n">
         <v>277.55</v>
@@ -3181,18 +2777,6 @@
       </c>
       <c r="V34" t="n">
         <v>0.25</v>
-      </c>
-      <c r="W34" t="n">
-        <v>2</v>
-      </c>
-      <c r="X34" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -3262,18 +2846,6 @@
       <c r="V35" t="n">
         <v>0.25</v>
       </c>
-      <c r="W35" t="n">
-        <v>2</v>
-      </c>
-      <c r="X35" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
@@ -3313,7 +2885,7 @@
         <v>2400</v>
       </c>
       <c r="M36" t="n">
-        <v>6000</v>
+        <v>6000.000000000001</v>
       </c>
       <c r="N36" t="n">
         <v>1572.7992</v>
@@ -3341,18 +2913,6 @@
       </c>
       <c r="V36" t="n">
         <v>0.25</v>
-      </c>
-      <c r="W36" t="n">
-        <v>2</v>
-      </c>
-      <c r="X36" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -3387,13 +2947,13 @@
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>2843.510625068056</v>
+        <v>3000</v>
       </c>
       <c r="L37" t="n">
-        <v>2274.808500054445</v>
+        <v>2400</v>
       </c>
       <c r="M37" t="n">
-        <v>5687.021250136112</v>
+        <v>6000.000000000001</v>
       </c>
       <c r="N37" t="n">
         <v>1586.046</v>
@@ -3421,18 +2981,6 @@
       </c>
       <c r="V37" t="n">
         <v>0.25</v>
-      </c>
-      <c r="W37" t="n">
-        <v>2</v>
-      </c>
-      <c r="X37" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -3467,13 +3015,13 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>3000</v>
+        <v>2843.510625068056</v>
       </c>
       <c r="L38" t="n">
-        <v>2400</v>
+        <v>2274.808500054445</v>
       </c>
       <c r="M38" t="n">
-        <v>6000.000000000001</v>
+        <v>5687.021250136112</v>
       </c>
       <c r="N38" t="n">
         <v>1613.9928</v>
@@ -3501,18 +3049,6 @@
       </c>
       <c r="V38" t="n">
         <v>0.25</v>
-      </c>
-      <c r="W38" t="n">
-        <v>2</v>
-      </c>
-      <c r="X38" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -3582,18 +3118,6 @@
       <c r="V39" t="n">
         <v>0.25</v>
       </c>
-      <c r="W39" t="n">
-        <v>2</v>
-      </c>
-      <c r="X39" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
@@ -3662,18 +3186,6 @@
       <c r="V40" t="n">
         <v>0.25</v>
       </c>
-      <c r="W40" t="n">
-        <v>2</v>
-      </c>
-      <c r="X40" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
@@ -3742,25 +3254,13 @@
       <c r="V41" t="n">
         <v>0.25</v>
       </c>
-      <c r="W41" t="n">
-        <v>2</v>
-      </c>
-      <c r="X41" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
         <v>40</v>
       </c>
       <c r="B42" t="n">
-        <v>912.4010874117912</v>
+        <v>912.4010874117926</v>
       </c>
       <c r="C42" t="n">
         <v>0</v>
@@ -3769,7 +3269,7 @@
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>662.632092745339</v>
+        <v>662.6320927453401</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -3778,7 +3278,7 @@
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>249.7689946664522</v>
+        <v>249.7689946664525</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -3796,10 +3296,10 @@
         <v>6000</v>
       </c>
       <c r="N42" t="n">
-        <v>889.6207072546607</v>
+        <v>889.6207072546597</v>
       </c>
       <c r="O42" t="n">
-        <v>20.3784379167257</v>
+        <v>20.37843791672568</v>
       </c>
       <c r="P42" t="n">
         <v>278.79</v>
@@ -3821,18 +3321,6 @@
       </c>
       <c r="V42" t="n">
         <v>0.25</v>
-      </c>
-      <c r="W42" t="n">
-        <v>2</v>
-      </c>
-      <c r="X42" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -3840,7 +3328,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="n">
-        <v>741.2357331899775</v>
+        <v>741.2357331899755</v>
       </c>
       <c r="C43" t="n">
         <v>0</v>
@@ -3849,7 +3337,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>553.7357331899771</v>
+        <v>553.7357331899756</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -3858,7 +3346,7 @@
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>187.5000000000004</v>
+        <v>187.4999999999999</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
@@ -3876,10 +3364,10 @@
         <v>6000</v>
       </c>
       <c r="N43" t="n">
-        <v>988.5714668100227</v>
+        <v>988.5714668100242</v>
       </c>
       <c r="O43" t="n">
-        <v>22.50589565873699</v>
+        <v>22.50589565873702</v>
       </c>
       <c r="P43" t="n">
         <v>278.55</v>
@@ -3901,18 +3389,6 @@
       </c>
       <c r="V43" t="n">
         <v>0.25</v>
-      </c>
-      <c r="W43" t="n">
-        <v>2</v>
-      </c>
-      <c r="X43" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -3982,18 +3458,6 @@
       <c r="V44" t="n">
         <v>0.25</v>
       </c>
-      <c r="W44" t="n">
-        <v>2</v>
-      </c>
-      <c r="X44" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
@@ -4062,18 +3526,6 @@
       <c r="V45" t="n">
         <v>0.25</v>
       </c>
-      <c r="W45" t="n">
-        <v>2</v>
-      </c>
-      <c r="X45" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
@@ -4142,18 +3594,6 @@
       <c r="V46" t="n">
         <v>0.25</v>
       </c>
-      <c r="W46" t="n">
-        <v>2</v>
-      </c>
-      <c r="X46" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
@@ -4222,18 +3662,6 @@
       <c r="V47" t="n">
         <v>0.16</v>
       </c>
-      <c r="W47" t="n">
-        <v>2</v>
-      </c>
-      <c r="X47" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
@@ -4302,18 +3730,6 @@
       <c r="V48" t="n">
         <v>0.16</v>
       </c>
-      <c r="W48" t="n">
-        <v>2</v>
-      </c>
-      <c r="X48" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
@@ -4382,25 +3798,13 @@
       <c r="V49" t="n">
         <v>0.16</v>
       </c>
-      <c r="W49" t="n">
-        <v>2</v>
-      </c>
-      <c r="X49" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
         <v>48</v>
       </c>
       <c r="B50" t="n">
-        <v>1156.671011549335</v>
+        <v>667.4339197923005</v>
       </c>
       <c r="C50" t="n">
         <v>0</v>
@@ -4409,7 +3813,7 @@
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>845.6152953313767</v>
+        <v>479.9339197923005</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -4418,7 +3822,7 @@
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>311.0557162179584</v>
+        <v>187.5</v>
       </c>
       <c r="I50" t="n">
         <v>0</v>
@@ -4436,10 +3840,10 @@
         <v>6000</v>
       </c>
       <c r="N50" t="n">
-        <v>545.9119046686233</v>
+        <v>911.5932802076995</v>
       </c>
       <c r="O50" t="n">
-        <v>12.05469440875814</v>
+        <v>20.12958194170857</v>
       </c>
       <c r="P50" t="n">
         <v>277.34</v>
@@ -4461,18 +3865,6 @@
       </c>
       <c r="V50" t="n">
         <v>0.16</v>
-      </c>
-      <c r="W50" t="n">
-        <v>2</v>
-      </c>
-      <c r="X50" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y50" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -4480,7 +3872,7 @@
         <v>49</v>
       </c>
       <c r="B51" t="n">
-        <v>0</v>
+        <v>742.4339197923005</v>
       </c>
       <c r="C51" t="n">
         <v>0</v>
@@ -4489,7 +3881,7 @@
         <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>0</v>
+        <v>554.9339197923005</v>
       </c>
       <c r="F51" t="n">
         <v>0</v>
@@ -4498,7 +3890,7 @@
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>0</v>
+        <v>187.5</v>
       </c>
       <c r="I51" t="n">
         <v>0</v>
@@ -4516,10 +3908,10 @@
         <v>6000</v>
       </c>
       <c r="N51" t="n">
-        <v>1375.332</v>
+        <v>820.3980802076996</v>
       </c>
       <c r="O51" t="n">
-        <v>30.39239821004367</v>
+        <v>18.12934269283907</v>
       </c>
       <c r="P51" t="n">
         <v>277.37</v>
@@ -4541,18 +3933,6 @@
       </c>
       <c r="V51" t="n">
         <v>0.16</v>
-      </c>
-      <c r="W51" t="n">
-        <v>2</v>
-      </c>
-      <c r="X51" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -4560,7 +3940,7 @@
         <v>50</v>
       </c>
       <c r="B52" t="n">
-        <v>667.4339197923005</v>
+        <v>0</v>
       </c>
       <c r="C52" t="n">
         <v>0</v>
@@ -4569,7 +3949,7 @@
         <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>479.9339197923004</v>
+        <v>0</v>
       </c>
       <c r="F52" t="n">
         <v>0</v>
@@ -4578,7 +3958,7 @@
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>187.5</v>
+        <v>0</v>
       </c>
       <c r="I52" t="n">
         <v>0</v>
@@ -4596,10 +3976,10 @@
         <v>6000</v>
       </c>
       <c r="N52" t="n">
-        <v>882.6132802076995</v>
+        <v>1362.5472</v>
       </c>
       <c r="O52" t="n">
-        <v>19.46064614740125</v>
+        <v>30.04265799410192</v>
       </c>
       <c r="P52" t="n">
         <v>277.28</v>
@@ -4621,18 +4001,6 @@
       </c>
       <c r="V52" t="n">
         <v>0.16</v>
-      </c>
-      <c r="W52" t="n">
-        <v>2</v>
-      </c>
-      <c r="X52" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y52" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z52" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -4640,7 +4008,7 @@
         <v>51</v>
       </c>
       <c r="B53" t="n">
-        <v>0</v>
+        <v>667.4339197923005</v>
       </c>
       <c r="C53" t="n">
         <v>0</v>
@@ -4649,7 +4017,7 @@
         <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>0</v>
+        <v>479.9339197923004</v>
       </c>
       <c r="F53" t="n">
         <v>0</v>
@@ -4658,7 +4026,7 @@
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>187.5</v>
       </c>
       <c r="I53" t="n">
         <v>0</v>
@@ -4676,10 +4044,10 @@
         <v>6000</v>
       </c>
       <c r="N53" t="n">
-        <v>1364.706</v>
+        <v>884.7720802076994</v>
       </c>
       <c r="O53" t="n">
-        <v>30.07533676758217</v>
+        <v>19.49857205493402</v>
       </c>
       <c r="P53" t="n">
         <v>277.26</v>
@@ -4701,18 +4069,6 @@
       </c>
       <c r="V53" t="n">
         <v>0.16</v>
-      </c>
-      <c r="W53" t="n">
-        <v>2</v>
-      </c>
-      <c r="X53" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y53" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z53" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -4782,18 +4138,6 @@
       <c r="V54" t="n">
         <v>0.16</v>
       </c>
-      <c r="W54" t="n">
-        <v>2</v>
-      </c>
-      <c r="X54" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y54" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z54" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
@@ -4862,25 +4206,13 @@
       <c r="V55" t="n">
         <v>0.16</v>
       </c>
-      <c r="W55" t="n">
-        <v>2</v>
-      </c>
-      <c r="X55" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y55" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z55" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
         <v>54</v>
       </c>
       <c r="B56" t="n">
-        <v>742.4339197922997</v>
+        <v>742.4339197923005</v>
       </c>
       <c r="C56" t="n">
         <v>0</v>
@@ -4889,7 +4221,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>554.9339197922999</v>
+        <v>554.9339197923005</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -4898,7 +4230,7 @@
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>187.4999999999998</v>
+        <v>187.5</v>
       </c>
       <c r="I56" t="n">
         <v>0</v>
@@ -4916,10 +4248,10 @@
         <v>6000</v>
       </c>
       <c r="N56" t="n">
-        <v>871.6296802077003</v>
+        <v>871.6296802076997</v>
       </c>
       <c r="O56" t="n">
-        <v>19.31428812470321</v>
+        <v>19.3142881247032</v>
       </c>
       <c r="P56" t="n">
         <v>277.48</v>
@@ -4941,18 +4273,6 @@
       </c>
       <c r="V56" t="n">
         <v>0.16</v>
-      </c>
-      <c r="W56" t="n">
-        <v>2</v>
-      </c>
-      <c r="X56" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y56" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z56" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -4960,7 +4280,7 @@
         <v>55</v>
       </c>
       <c r="B57" t="n">
-        <v>995.7798149559416</v>
+        <v>742.5829869206714</v>
       </c>
       <c r="C57" t="n">
         <v>0</v>
@@ -4969,7 +4289,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>744.2978846092358</v>
+        <v>555.0453403560083</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -4978,7 +4298,7 @@
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>251.4819303467058</v>
+        <v>187.5376465646631</v>
       </c>
       <c r="I57" t="n">
         <v>0</v>
@@ -4996,10 +4316,10 @@
         <v>6000</v>
       </c>
       <c r="N57" t="n">
-        <v>740.9817153907641</v>
+        <v>930.2342596439915</v>
       </c>
       <c r="O57" t="n">
-        <v>16.52225241966138</v>
+        <v>20.74216533015199</v>
       </c>
       <c r="P57" t="n">
         <v>277.73</v>
@@ -5021,18 +4341,6 @@
       </c>
       <c r="V57" t="n">
         <v>0.16</v>
-      </c>
-      <c r="W57" t="n">
-        <v>2</v>
-      </c>
-      <c r="X57" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y57" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z57" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -5102,25 +4410,13 @@
       <c r="V58" t="n">
         <v>0.25</v>
       </c>
-      <c r="W58" t="n">
-        <v>2</v>
-      </c>
-      <c r="X58" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y58" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z58" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
         <v>57</v>
       </c>
       <c r="B59" t="n">
-        <v>667.4339197923003</v>
+        <v>667.4339197923005</v>
       </c>
       <c r="C59" t="n">
         <v>0</v>
@@ -5129,7 +4425,7 @@
         <v>0</v>
       </c>
       <c r="E59" t="n">
-        <v>479.9339197923003</v>
+        <v>479.9339197923005</v>
       </c>
       <c r="F59" t="n">
         <v>0</v>
@@ -5156,7 +4452,7 @@
         <v>6000</v>
       </c>
       <c r="N59" t="n">
-        <v>1056.5604802077</v>
+        <v>1056.560480207699</v>
       </c>
       <c r="O59" t="n">
         <v>23.76162105493534</v>
@@ -5181,18 +4477,6 @@
       </c>
       <c r="V59" t="n">
         <v>0.25</v>
-      </c>
-      <c r="W59" t="n">
-        <v>2</v>
-      </c>
-      <c r="X59" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y59" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z59" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -5200,7 +4484,7 @@
         <v>58</v>
       </c>
       <c r="B60" t="n">
-        <v>742.4339197922957</v>
+        <v>742.4339197923005</v>
       </c>
       <c r="C60" t="n">
         <v>0</v>
@@ -5209,7 +4493,7 @@
         <v>0</v>
       </c>
       <c r="E60" t="n">
-        <v>554.9339197922969</v>
+        <v>554.9339197923005</v>
       </c>
       <c r="F60" t="n">
         <v>0</v>
@@ -5218,7 +4502,7 @@
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>187.4999999999988</v>
+        <v>187.5</v>
       </c>
       <c r="I60" t="n">
         <v>0</v>
@@ -5236,10 +4520,10 @@
         <v>6000</v>
       </c>
       <c r="N60" t="n">
-        <v>1054.674080207703</v>
+        <v>1054.674080207699</v>
       </c>
       <c r="O60" t="n">
-        <v>23.80955679561368</v>
+        <v>23.80955679561361</v>
       </c>
       <c r="P60" t="n">
         <v>278.22</v>
@@ -5261,18 +4545,6 @@
       </c>
       <c r="V60" t="n">
         <v>0.25</v>
-      </c>
-      <c r="W60" t="n">
-        <v>2</v>
-      </c>
-      <c r="X60" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y60" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z60" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -5280,7 +4552,7 @@
         <v>59</v>
       </c>
       <c r="B61" t="n">
-        <v>742.4339197923005</v>
+        <v>742.4339197923003</v>
       </c>
       <c r="C61" t="n">
         <v>0</v>
@@ -5289,7 +4561,7 @@
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>554.9339197923005</v>
+        <v>554.9339197923003</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
@@ -5341,18 +4613,6 @@
       </c>
       <c r="V61" t="n">
         <v>0.25</v>
-      </c>
-      <c r="W61" t="n">
-        <v>2</v>
-      </c>
-      <c r="X61" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y61" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z61" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -5422,18 +4682,6 @@
       <c r="V62" t="n">
         <v>0.25</v>
       </c>
-      <c r="W62" t="n">
-        <v>2</v>
-      </c>
-      <c r="X62" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y62" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z62" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
@@ -5502,25 +4750,13 @@
       <c r="V63" t="n">
         <v>0.25</v>
       </c>
-      <c r="W63" t="n">
-        <v>2</v>
-      </c>
-      <c r="X63" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y63" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z63" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
         <v>62</v>
       </c>
       <c r="B64" t="n">
-        <v>760.1172661791545</v>
+        <v>760.1172661791234</v>
       </c>
       <c r="C64" t="n">
         <v>0</v>
@@ -5529,7 +4765,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>549.2102975799871</v>
+        <v>549.2102975799638</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -5538,7 +4774,7 @@
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>210.9069685991674</v>
+        <v>210.9069685991595</v>
       </c>
       <c r="I64" t="n">
         <v>0</v>
@@ -5556,10 +4792,10 @@
         <v>6000</v>
       </c>
       <c r="N64" t="n">
-        <v>1001.799302420012</v>
+        <v>1001.799302420036</v>
       </c>
       <c r="O64" t="n">
-        <v>23.12089091930906</v>
+        <v>23.1208909193096</v>
       </c>
       <c r="P64" t="n">
         <v>279.08</v>
@@ -5581,18 +4817,6 @@
       </c>
       <c r="V64" t="n">
         <v>0.25</v>
-      </c>
-      <c r="W64" t="n">
-        <v>2</v>
-      </c>
-      <c r="X64" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y64" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z64" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -5662,18 +4886,6 @@
       <c r="V65" t="n">
         <v>0.25</v>
       </c>
-      <c r="W65" t="n">
-        <v>2</v>
-      </c>
-      <c r="X65" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y65" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z65" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
@@ -5742,25 +4954,13 @@
       <c r="V66" t="n">
         <v>0.25</v>
       </c>
-      <c r="W66" t="n">
-        <v>2</v>
-      </c>
-      <c r="X66" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y66" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z66" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
         <v>65</v>
       </c>
       <c r="B67" t="n">
-        <v>865.9861747255941</v>
+        <v>865.9861747256231</v>
       </c>
       <c r="C67" t="n">
         <v>0</v>
@@ -5769,7 +4969,7 @@
         <v>0</v>
       </c>
       <c r="E67" t="n">
-        <v>628.3422537549474</v>
+        <v>628.3422537549691</v>
       </c>
       <c r="F67" t="n">
         <v>0</v>
@@ -5778,7 +4978,7 @@
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>237.6439209706467</v>
+        <v>237.643920970654</v>
       </c>
       <c r="I67" t="n">
         <v>0</v>
@@ -5796,10 +4996,10 @@
         <v>6000</v>
       </c>
       <c r="N67" t="n">
-        <v>895.1657462450522</v>
+        <v>895.1657462450305</v>
       </c>
       <c r="O67" t="n">
-        <v>20.7731216857934</v>
+        <v>20.77312168579289</v>
       </c>
       <c r="P67" t="n">
         <v>279.29</v>
@@ -5821,18 +5021,6 @@
       </c>
       <c r="V67" t="n">
         <v>0.25</v>
-      </c>
-      <c r="W67" t="n">
-        <v>2</v>
-      </c>
-      <c r="X67" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y67" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z67" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -5902,18 +5090,6 @@
       <c r="V68" t="n">
         <v>0.25</v>
       </c>
-      <c r="W68" t="n">
-        <v>2</v>
-      </c>
-      <c r="X68" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y68" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z68" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
@@ -5982,18 +5158,6 @@
       <c r="V69" t="n">
         <v>0.25</v>
       </c>
-      <c r="W69" t="n">
-        <v>2</v>
-      </c>
-      <c r="X69" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y69" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z69" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
@@ -6062,18 +5226,6 @@
       <c r="V70" t="n">
         <v>0.25</v>
       </c>
-      <c r="W70" t="n">
-        <v>2</v>
-      </c>
-      <c r="X70" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y70" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z70" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
@@ -6107,13 +5259,13 @@
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>3000</v>
+        <v>3000.000000000002</v>
       </c>
       <c r="L71" t="n">
-        <v>2400</v>
+        <v>2400.000000000001</v>
       </c>
       <c r="M71" t="n">
-        <v>6000</v>
+        <v>6000.000000000004</v>
       </c>
       <c r="N71" t="n">
         <v>856.2876802076994</v>
@@ -6141,18 +5293,6 @@
       </c>
       <c r="V71" t="n">
         <v>0.16</v>
-      </c>
-      <c r="W71" t="n">
-        <v>2</v>
-      </c>
-      <c r="X71" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y71" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z71" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -6222,18 +5362,6 @@
       <c r="V72" t="n">
         <v>0.16</v>
       </c>
-      <c r="W72" t="n">
-        <v>2</v>
-      </c>
-      <c r="X72" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y72" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z72" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
@@ -6302,25 +5430,13 @@
       <c r="V73" t="n">
         <v>0.16</v>
       </c>
-      <c r="W73" t="n">
-        <v>2</v>
-      </c>
-      <c r="X73" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y73" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z73" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
         <v>72</v>
       </c>
       <c r="B74" t="n">
-        <v>794.3736219000764</v>
+        <v>794.373621900074</v>
       </c>
       <c r="C74" t="n">
         <v>0</v>
@@ -6329,7 +5445,7 @@
         <v>0</v>
       </c>
       <c r="E74" t="n">
-        <v>576.8897916428517</v>
+        <v>576.8897916428499</v>
       </c>
       <c r="F74" t="n">
         <v>0</v>
@@ -6338,7 +5454,7 @@
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>217.4838302572247</v>
+        <v>217.4838302572241</v>
       </c>
       <c r="I74" t="n">
         <v>0</v>
@@ -6356,10 +5472,10 @@
         <v>6000</v>
       </c>
       <c r="N74" t="n">
-        <v>762.4062083571481</v>
+        <v>762.4062083571499</v>
       </c>
       <c r="O74" t="n">
-        <v>17.46435020861637</v>
+        <v>17.46435020861642</v>
       </c>
       <c r="P74" t="n">
         <v>278.79</v>
@@ -6381,18 +5497,6 @@
       </c>
       <c r="V74" t="n">
         <v>0.16</v>
-      </c>
-      <c r="W74" t="n">
-        <v>2</v>
-      </c>
-      <c r="X74" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y74" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z74" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -6433,7 +5537,7 @@
         <v>2400</v>
       </c>
       <c r="M75" t="n">
-        <v>5999.999999999999</v>
+        <v>6000</v>
       </c>
       <c r="N75" t="n">
         <v>1340.7408</v>
@@ -6461,18 +5565,6 @@
       </c>
       <c r="V75" t="n">
         <v>0.16</v>
-      </c>
-      <c r="W75" t="n">
-        <v>2</v>
-      </c>
-      <c r="X75" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y75" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z75" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -6542,18 +5634,6 @@
       <c r="V76" t="n">
         <v>0.16</v>
       </c>
-      <c r="W76" t="n">
-        <v>2</v>
-      </c>
-      <c r="X76" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y76" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z76" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
@@ -6622,18 +5702,6 @@
       <c r="V77" t="n">
         <v>0.16</v>
       </c>
-      <c r="W77" t="n">
-        <v>2</v>
-      </c>
-      <c r="X77" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y77" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z77" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
@@ -6702,25 +5770,13 @@
       <c r="V78" t="n">
         <v>0.16</v>
       </c>
-      <c r="W78" t="n">
-        <v>2</v>
-      </c>
-      <c r="X78" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y78" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z78" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
         <v>77</v>
       </c>
       <c r="B79" t="n">
-        <v>826.1136248586828</v>
+        <v>752.1163110394165</v>
       </c>
       <c r="C79" t="n">
         <v>0</v>
@@ -6729,7 +5785,7 @@
         <v>0</v>
       </c>
       <c r="E79" t="n">
-        <v>600.6896670867465</v>
+        <v>545.2036340709936</v>
       </c>
       <c r="F79" t="n">
         <v>0</v>
@@ -6738,7 +5794,7 @@
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>225.4239577719364</v>
+        <v>206.9126769684229</v>
       </c>
       <c r="I79" t="n">
         <v>0</v>
@@ -6756,10 +5812,10 @@
         <v>6000</v>
       </c>
       <c r="N79" t="n">
-        <v>763.7559329132536</v>
+        <v>819.2419659290064</v>
       </c>
       <c r="O79" t="n">
-        <v>17.22013263994709</v>
+        <v>18.47115643828434</v>
       </c>
       <c r="P79" t="n">
         <v>278.17</v>
@@ -6781,18 +5837,6 @@
       </c>
       <c r="V79" t="n">
         <v>0.16</v>
-      </c>
-      <c r="W79" t="n">
-        <v>2</v>
-      </c>
-      <c r="X79" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y79" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z79" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="80">
@@ -6862,25 +5906,13 @@
       <c r="V80" t="n">
         <v>0.16</v>
       </c>
-      <c r="W80" t="n">
-        <v>2</v>
-      </c>
-      <c r="X80" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y80" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z80" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
         <v>79</v>
       </c>
       <c r="B81" t="n">
-        <v>749.5157406114781</v>
+        <v>749.5157406114762</v>
       </c>
       <c r="C81" t="n">
         <v>0</v>
@@ -6889,7 +5921,7 @@
         <v>0</v>
       </c>
       <c r="E81" t="n">
-        <v>562.0157406114777</v>
+        <v>562.0157406114762</v>
       </c>
       <c r="F81" t="n">
         <v>0</v>
@@ -6898,7 +5930,7 @@
         <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>187.5000000000005</v>
+        <v>187.5</v>
       </c>
       <c r="I81" t="n">
         <v>0</v>
@@ -6916,10 +5948,10 @@
         <v>6000</v>
       </c>
       <c r="N81" t="n">
-        <v>915.6534593885224</v>
+        <v>915.6534593885239</v>
       </c>
       <c r="O81" t="n">
-        <v>20.58746992807449</v>
+        <v>20.58746992807452</v>
       </c>
       <c r="P81" t="n">
         <v>278.06</v>
@@ -6941,18 +5973,6 @@
       </c>
       <c r="V81" t="n">
         <v>0.16</v>
-      </c>
-      <c r="W81" t="n">
-        <v>2</v>
-      </c>
-      <c r="X81" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y81" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z81" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="82">
@@ -6960,7 +5980,7 @@
         <v>80</v>
       </c>
       <c r="B82" t="n">
-        <v>-5.623864908597788e-12</v>
+        <v>0</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
@@ -6969,7 +5989,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>-4.216990291792789e-12</v>
+        <v>0</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -6978,7 +5998,7 @@
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>-1.406874616804998e-12</v>
+        <v>0</v>
       </c>
       <c r="I82" t="n">
         <v>0</v>
@@ -6996,10 +6016,10 @@
         <v>6000</v>
       </c>
       <c r="N82" t="n">
-        <v>1515.410400000004</v>
+        <v>1515.4104</v>
       </c>
       <c r="O82" t="n">
-        <v>34.03791223292258</v>
+        <v>34.03791223292248</v>
       </c>
       <c r="P82" t="n">
         <v>278.02</v>
@@ -7021,18 +6041,6 @@
       </c>
       <c r="V82" t="n">
         <v>0.25</v>
-      </c>
-      <c r="W82" t="n">
-        <v>2</v>
-      </c>
-      <c r="X82" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y82" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z82" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -7040,7 +6048,7 @@
         <v>81</v>
       </c>
       <c r="B83" t="n">
-        <v>674.5157406114762</v>
+        <v>674.5157406114776</v>
       </c>
       <c r="C83" t="n">
         <v>0</v>
@@ -7049,7 +6057,7 @@
         <v>0</v>
       </c>
       <c r="E83" t="n">
-        <v>487.0157406114762</v>
+        <v>487.0157406114772</v>
       </c>
       <c r="F83" t="n">
         <v>0</v>
@@ -7058,7 +6066,7 @@
         <v>0</v>
       </c>
       <c r="H83" t="n">
-        <v>187.5</v>
+        <v>187.5000000000003</v>
       </c>
       <c r="I83" t="n">
         <v>0</v>
@@ -7076,10 +6084,10 @@
         <v>6000</v>
       </c>
       <c r="N83" t="n">
-        <v>1123.146659388524</v>
+        <v>1123.146659388523</v>
       </c>
       <c r="O83" t="n">
-        <v>25.33604013960127</v>
+        <v>25.33604013960124</v>
       </c>
       <c r="P83" t="n">
         <v>278.19</v>
@@ -7101,18 +6109,6 @@
       </c>
       <c r="V83" t="n">
         <v>0.25</v>
-      </c>
-      <c r="W83" t="n">
-        <v>2</v>
-      </c>
-      <c r="X83" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y83" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z83" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="84">
@@ -7120,7 +6116,7 @@
         <v>82</v>
       </c>
       <c r="B84" t="n">
-        <v>829.5521743424324</v>
+        <v>749.5157406114762</v>
       </c>
       <c r="C84" t="n">
         <v>0</v>
@@ -7129,7 +6125,7 @@
         <v>0</v>
       </c>
       <c r="E84" t="n">
-        <v>622.0301380976548</v>
+        <v>562.0157406114762</v>
       </c>
       <c r="F84" t="n">
         <v>0</v>
@@ -7138,7 +6134,7 @@
         <v>0</v>
       </c>
       <c r="H84" t="n">
-        <v>207.5220362447776</v>
+        <v>187.5</v>
       </c>
       <c r="I84" t="n">
         <v>0</v>
@@ -7156,10 +6152,10 @@
         <v>6000</v>
       </c>
       <c r="N84" t="n">
-        <v>1040.581861902345</v>
+        <v>1100.596259388524</v>
       </c>
       <c r="O84" t="n">
-        <v>23.6536196374915</v>
+        <v>25.01781575015112</v>
       </c>
       <c r="P84" t="n">
         <v>278.49</v>
@@ -7181,18 +6177,6 @@
       </c>
       <c r="V84" t="n">
         <v>0.25</v>
-      </c>
-      <c r="W84" t="n">
-        <v>2</v>
-      </c>
-      <c r="X84" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y84" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z84" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="85">
@@ -7200,7 +6184,7 @@
         <v>83</v>
       </c>
       <c r="B85" t="n">
-        <v>0</v>
+        <v>749.5157406114762</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
@@ -7209,7 +6193,7 @@
         <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>0</v>
+        <v>562.0157406114762</v>
       </c>
       <c r="F85" t="n">
         <v>0</v>
@@ -7218,7 +6202,7 @@
         <v>0</v>
       </c>
       <c r="H85" t="n">
-        <v>0</v>
+        <v>187.5</v>
       </c>
       <c r="I85" t="n">
         <v>0</v>
@@ -7236,10 +6220,10 @@
         <v>6000</v>
       </c>
       <c r="N85" t="n">
-        <v>1519.77</v>
+        <v>957.7542593885238</v>
       </c>
       <c r="O85" t="n">
-        <v>34.71478742540614</v>
+        <v>21.87714951634122</v>
       </c>
       <c r="P85" t="n">
         <v>278.6799999999999</v>
@@ -7261,18 +6245,6 @@
       </c>
       <c r="V85" t="n">
         <v>0.25</v>
-      </c>
-      <c r="W85" t="n">
-        <v>2</v>
-      </c>
-      <c r="X85" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y85" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z85" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="86">
@@ -7280,7 +6252,7 @@
         <v>84</v>
       </c>
       <c r="B86" t="n">
-        <v>1091.958964238324</v>
+        <v>749.5157406114762</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
@@ -7289,7 +6261,7 @@
         <v>0</v>
       </c>
       <c r="E86" t="n">
-        <v>800.0307311952413</v>
+        <v>562.0157406114762</v>
       </c>
       <c r="F86" t="n">
         <v>0</v>
@@ -7298,7 +6270,7 @@
         <v>0</v>
       </c>
       <c r="H86" t="n">
-        <v>291.9282330430827</v>
+        <v>187.5</v>
       </c>
       <c r="I86" t="n">
         <v>0</v>
@@ -7316,10 +6288,10 @@
         <v>6000</v>
       </c>
       <c r="N86" t="n">
-        <v>753.1964688047585</v>
+        <v>991.2114593885236</v>
       </c>
       <c r="O86" t="n">
-        <v>17.31585651600111</v>
+        <v>22.78777997329784</v>
       </c>
       <c r="P86" t="n">
         <v>278.9299999999999</v>
@@ -7341,18 +6313,6 @@
       </c>
       <c r="V86" t="n">
         <v>0.25</v>
-      </c>
-      <c r="W86" t="n">
-        <v>2</v>
-      </c>
-      <c r="X86" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y86" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z86" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="87">
@@ -7360,7 +6320,7 @@
         <v>85</v>
       </c>
       <c r="B87" t="n">
-        <v>749.5157406114762</v>
+        <v>0</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
@@ -7369,7 +6329,7 @@
         <v>0</v>
       </c>
       <c r="E87" t="n">
-        <v>562.0157406114762</v>
+        <v>0</v>
       </c>
       <c r="F87" t="n">
         <v>0</v>
@@ -7378,7 +6338,7 @@
         <v>0</v>
       </c>
       <c r="H87" t="n">
-        <v>187.5</v>
+        <v>0</v>
       </c>
       <c r="I87" t="n">
         <v>0</v>
@@ -7396,10 +6356,10 @@
         <v>6000</v>
       </c>
       <c r="N87" t="n">
-        <v>987.7926593885237</v>
+        <v>1549.8084</v>
       </c>
       <c r="O87" t="n">
-        <v>22.70331046946932</v>
+        <v>35.6206142442612</v>
       </c>
       <c r="P87" t="n">
         <v>278.92</v>
@@ -7421,18 +6381,6 @@
       </c>
       <c r="V87" t="n">
         <v>0.25</v>
-      </c>
-      <c r="W87" t="n">
-        <v>2</v>
-      </c>
-      <c r="X87" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y87" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z87" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="88">
@@ -7440,7 +6388,7 @@
         <v>86</v>
       </c>
       <c r="B88" t="n">
-        <v>0</v>
+        <v>799.8802587031403</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
@@ -7449,7 +6397,7 @@
         <v>0</v>
       </c>
       <c r="E88" t="n">
-        <v>0</v>
+        <v>581.018879790657</v>
       </c>
       <c r="F88" t="n">
         <v>0</v>
@@ -7458,7 +6406,7 @@
         <v>0</v>
       </c>
       <c r="H88" t="n">
-        <v>0</v>
+        <v>218.8613789124832</v>
       </c>
       <c r="I88" t="n">
         <v>0</v>
@@ -7476,10 +6424,10 @@
         <v>6000</v>
       </c>
       <c r="N88" t="n">
-        <v>1562.1648</v>
+        <v>981.1459202093428</v>
       </c>
       <c r="O88" t="n">
-        <v>36.13821756983399</v>
+        <v>22.69726262701619</v>
       </c>
       <c r="P88" t="n">
         <v>279.17</v>
@@ -7501,18 +6449,6 @@
       </c>
       <c r="V88" t="n">
         <v>0.25</v>
-      </c>
-      <c r="W88" t="n">
-        <v>2</v>
-      </c>
-      <c r="X88" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y88" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z88" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="89">
@@ -7582,18 +6518,6 @@
       <c r="V89" t="n">
         <v>0.25</v>
       </c>
-      <c r="W89" t="n">
-        <v>2</v>
-      </c>
-      <c r="X89" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y89" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z89" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
@@ -7662,18 +6586,6 @@
       <c r="V90" t="n">
         <v>0.25</v>
       </c>
-      <c r="W90" t="n">
-        <v>2</v>
-      </c>
-      <c r="X90" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y90" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z90" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
@@ -7742,18 +6654,6 @@
       <c r="V91" t="n">
         <v>0.25</v>
       </c>
-      <c r="W91" t="n">
-        <v>2</v>
-      </c>
-      <c r="X91" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y91" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z91" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
@@ -7822,25 +6722,13 @@
       <c r="V92" t="n">
         <v>0.25</v>
       </c>
-      <c r="W92" t="n">
-        <v>2</v>
-      </c>
-      <c r="X92" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y92" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z92" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
         <v>91</v>
       </c>
       <c r="B93" t="n">
-        <v>977.9190281375501</v>
+        <v>674.5157406114757</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
@@ -7849,7 +6737,7 @@
         <v>0</v>
       </c>
       <c r="E93" t="n">
-        <v>714.5191993164397</v>
+        <v>487.0157406114758</v>
       </c>
       <c r="F93" t="n">
         <v>0</v>
@@ -7858,7 +6746,7 @@
         <v>0</v>
       </c>
       <c r="H93" t="n">
-        <v>263.3998288211104</v>
+        <v>187.4999999999999</v>
       </c>
       <c r="I93" t="n">
         <v>0</v>
@@ -7876,10 +6764,10 @@
         <v>6000</v>
       </c>
       <c r="N93" t="n">
-        <v>767.2576006835604</v>
+        <v>994.7610593885242</v>
       </c>
       <c r="O93" t="n">
-        <v>17.29031212808023</v>
+        <v>22.41715063410759</v>
       </c>
       <c r="P93" t="n">
         <v>278.15</v>
@@ -7901,18 +6789,6 @@
       </c>
       <c r="V93" t="n">
         <v>0.25</v>
-      </c>
-      <c r="W93" t="n">
-        <v>2</v>
-      </c>
-      <c r="X93" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y93" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z93" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="94">
@@ -7982,25 +6858,13 @@
       <c r="V94" t="n">
         <v>0.25</v>
       </c>
-      <c r="W94" t="n">
-        <v>2</v>
-      </c>
-      <c r="X94" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y94" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z94" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
         <v>93</v>
       </c>
       <c r="B95" t="n">
-        <v>1299.254861119658</v>
+        <v>1299.254861119656</v>
       </c>
       <c r="C95" t="n">
         <v>0</v>
@@ -8009,7 +6873,7 @@
         <v>0</v>
       </c>
       <c r="E95" t="n">
-        <v>955.4691705753622</v>
+        <v>955.4691705753605</v>
       </c>
       <c r="F95" t="n">
         <v>0</v>
@@ -8018,7 +6882,7 @@
         <v>0</v>
       </c>
       <c r="H95" t="n">
-        <v>343.7856905442962</v>
+        <v>343.7856905442956</v>
       </c>
       <c r="I95" t="n">
         <v>0</v>
@@ -8027,19 +6891,19 @@
         <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>2999.999999999998</v>
+        <v>3000</v>
       </c>
       <c r="L95" t="n">
-        <v>2399.999999999998</v>
+        <v>2400</v>
       </c>
       <c r="M95" t="n">
-        <v>5999.999999999995</v>
+        <v>6000</v>
       </c>
       <c r="N95" t="n">
-        <v>420.8540294246376</v>
+        <v>420.8540294246393</v>
       </c>
       <c r="O95" t="n">
-        <v>9.384113482906237</v>
+        <v>9.384113482906274</v>
       </c>
       <c r="P95" t="n">
         <v>277.73</v>
@@ -8061,18 +6925,6 @@
       </c>
       <c r="V95" t="n">
         <v>0.16</v>
-      </c>
-      <c r="W95" t="n">
-        <v>2</v>
-      </c>
-      <c r="X95" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y95" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z95" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="96">
@@ -8142,18 +6994,6 @@
       <c r="V96" t="n">
         <v>0.16</v>
       </c>
-      <c r="W96" t="n">
-        <v>2</v>
-      </c>
-      <c r="X96" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y96" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z96" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
@@ -8222,25 +7062,13 @@
       <c r="V97" t="n">
         <v>0.16</v>
       </c>
-      <c r="W97" t="n">
-        <v>2</v>
-      </c>
-      <c r="X97" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y97" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z97" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
         <v>96</v>
       </c>
       <c r="B98" t="n">
-        <v>903.9638853370484</v>
+        <v>903.9638853370489</v>
       </c>
       <c r="C98" t="n">
         <v>0</v>
@@ -8249,7 +7077,7 @@
         <v>0</v>
       </c>
       <c r="E98" t="n">
-        <v>659.1844481742056</v>
+        <v>659.184448174206</v>
       </c>
       <c r="F98" t="n">
         <v>0</v>
@@ -8258,7 +7086,7 @@
         <v>0</v>
       </c>
       <c r="H98" t="n">
-        <v>244.7794371628428</v>
+        <v>244.779437162843</v>
       </c>
       <c r="I98" t="n">
         <v>0</v>
@@ -8276,7 +7104,7 @@
         <v>6000</v>
       </c>
       <c r="N98" t="n">
-        <v>658.0699518257944</v>
+        <v>658.0699518257941</v>
       </c>
       <c r="O98" t="n">
         <v>14.53134123107553</v>
@@ -8301,18 +7129,6 @@
       </c>
       <c r="V98" t="n">
         <v>0.16</v>
-      </c>
-      <c r="W98" t="n">
-        <v>2</v>
-      </c>
-      <c r="X98" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y98" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z98" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="99">
@@ -8382,18 +7198,6 @@
       <c r="V99" t="n">
         <v>0.16</v>
       </c>
-      <c r="W99" t="n">
-        <v>2</v>
-      </c>
-      <c r="X99" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y99" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z99" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
@@ -8462,18 +7266,6 @@
       <c r="V100" t="n">
         <v>0.16</v>
       </c>
-      <c r="W100" t="n">
-        <v>2</v>
-      </c>
-      <c r="X100" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y100" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z100" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
@@ -8542,18 +7334,6 @@
       <c r="V101" t="n">
         <v>0.16</v>
       </c>
-      <c r="W101" t="n">
-        <v>2</v>
-      </c>
-      <c r="X101" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y101" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z101" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
@@ -8578,7 +7358,7 @@
         <v>0</v>
       </c>
       <c r="H102" t="n">
-        <v>187.4999999999997</v>
+        <v>187.4999999999996</v>
       </c>
       <c r="I102" t="n">
         <v>0</v>
@@ -8621,18 +7401,6 @@
       </c>
       <c r="V102" t="n">
         <v>0.16</v>
-      </c>
-      <c r="W102" t="n">
-        <v>2</v>
-      </c>
-      <c r="X102" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y102" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z102" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="103">
@@ -8702,25 +7470,13 @@
       <c r="V103" t="n">
         <v>0.16</v>
       </c>
-      <c r="W103" t="n">
-        <v>2</v>
-      </c>
-      <c r="X103" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y103" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z103" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
         <v>102</v>
       </c>
       <c r="B104" t="n">
-        <v>804.1215219563759</v>
+        <v>804.1215219563755</v>
       </c>
       <c r="C104" t="n">
         <v>0</v>
@@ -8729,7 +7485,7 @@
         <v>0</v>
       </c>
       <c r="E104" t="n">
-        <v>603.0595456126391</v>
+        <v>603.0595456126389</v>
       </c>
       <c r="F104" t="n">
         <v>0</v>
@@ -8756,10 +7512,10 @@
         <v>6000</v>
       </c>
       <c r="N104" t="n">
-        <v>819.2704543873608</v>
+        <v>819.270454387361</v>
       </c>
       <c r="O104" t="n">
-        <v>17.93941052442559</v>
+        <v>17.9394105244256</v>
       </c>
       <c r="P104" t="n">
         <v>277</v>
@@ -8781,18 +7537,6 @@
       </c>
       <c r="V104" t="n">
         <v>0.16</v>
-      </c>
-      <c r="W104" t="n">
-        <v>2</v>
-      </c>
-      <c r="X104" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y104" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z104" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="105">
@@ -8800,7 +7544,7 @@
         <v>103</v>
       </c>
       <c r="B105" t="n">
-        <v>847.2646275294481</v>
+        <v>847.2646275294469</v>
       </c>
       <c r="C105" t="n">
         <v>0</v>
@@ -8809,7 +7553,7 @@
         <v>0</v>
       </c>
       <c r="E105" t="n">
-        <v>635.4151795968102</v>
+        <v>635.4151795968093</v>
       </c>
       <c r="F105" t="n">
         <v>0</v>
@@ -8818,7 +7562,7 @@
         <v>0</v>
       </c>
       <c r="H105" t="n">
-        <v>211.849447932638</v>
+        <v>211.8494479326376</v>
       </c>
       <c r="I105" t="n">
         <v>0</v>
@@ -8836,10 +7580,10 @@
         <v>6000</v>
       </c>
       <c r="N105" t="n">
-        <v>837.0124204031898</v>
+        <v>837.0124204031907</v>
       </c>
       <c r="O105" t="n">
-        <v>18.29185500922096</v>
+        <v>18.29185500922098</v>
       </c>
       <c r="P105" t="n">
         <v>276.92</v>
@@ -8861,18 +7605,6 @@
       </c>
       <c r="V105" t="n">
         <v>0.16</v>
-      </c>
-      <c r="W105" t="n">
-        <v>2</v>
-      </c>
-      <c r="X105" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y105" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z105" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="106">
@@ -8880,7 +7612,7 @@
         <v>104</v>
       </c>
       <c r="B106" t="n">
-        <v>749.8821413605247</v>
+        <v>749.882141360526</v>
       </c>
       <c r="C106" t="n">
         <v>0</v>
@@ -8889,7 +7621,7 @@
         <v>0</v>
       </c>
       <c r="E106" t="n">
-        <v>562.3821413605247</v>
+        <v>562.3821413605257</v>
       </c>
       <c r="F106" t="n">
         <v>0</v>
@@ -8898,7 +7630,7 @@
         <v>0</v>
       </c>
       <c r="H106" t="n">
-        <v>187.5</v>
+        <v>187.5000000000003</v>
       </c>
       <c r="I106" t="n">
         <v>0</v>
@@ -8916,10 +7648,10 @@
         <v>6000</v>
       </c>
       <c r="N106" t="n">
-        <v>955.2542586394752</v>
+        <v>955.2542586394742</v>
       </c>
       <c r="O106" t="n">
-        <v>20.90672193558887</v>
+        <v>20.90672193558884</v>
       </c>
       <c r="P106" t="n">
         <v>276.98</v>
@@ -8941,18 +7673,6 @@
       </c>
       <c r="V106" t="n">
         <v>0.25</v>
-      </c>
-      <c r="W106" t="n">
-        <v>2</v>
-      </c>
-      <c r="X106" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y106" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z106" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="107">
@@ -8960,7 +7680,7 @@
         <v>105</v>
       </c>
       <c r="B107" t="n">
-        <v>749.8821413605247</v>
+        <v>0</v>
       </c>
       <c r="C107" t="n">
         <v>0</v>
@@ -8969,7 +7689,7 @@
         <v>0</v>
       </c>
       <c r="E107" t="n">
-        <v>562.3821413605247</v>
+        <v>0</v>
       </c>
       <c r="F107" t="n">
         <v>0</v>
@@ -8978,7 +7698,7 @@
         <v>0</v>
       </c>
       <c r="H107" t="n">
-        <v>187.5</v>
+        <v>0</v>
       </c>
       <c r="I107" t="n">
         <v>0</v>
@@ -8996,10 +7716,10 @@
         <v>6000</v>
       </c>
       <c r="N107" t="n">
-        <v>927.7358586394753</v>
+        <v>1490.118</v>
       </c>
       <c r="O107" t="n">
-        <v>20.33950909595998</v>
+        <v>32.66907097835021</v>
       </c>
       <c r="P107" t="n">
         <v>277.05</v>
@@ -9021,18 +7741,6 @@
       </c>
       <c r="V107" t="n">
         <v>0.25</v>
-      </c>
-      <c r="W107" t="n">
-        <v>2</v>
-      </c>
-      <c r="X107" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y107" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z107" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="108">
@@ -9040,7 +7748,7 @@
         <v>106</v>
       </c>
       <c r="B108" t="n">
-        <v>0</v>
+        <v>674.8821413605247</v>
       </c>
       <c r="C108" t="n">
         <v>0</v>
@@ -9049,7 +7757,7 @@
         <v>0</v>
       </c>
       <c r="E108" t="n">
-        <v>0</v>
+        <v>487.3821413605247</v>
       </c>
       <c r="F108" t="n">
         <v>0</v>
@@ -9058,7 +7766,7 @@
         <v>0</v>
       </c>
       <c r="H108" t="n">
-        <v>0</v>
+        <v>187.5</v>
       </c>
       <c r="I108" t="n">
         <v>0</v>
@@ -9076,10 +7784,10 @@
         <v>6000</v>
       </c>
       <c r="N108" t="n">
-        <v>2400</v>
+        <v>1912.617858639475</v>
       </c>
       <c r="O108" t="n">
-        <v>53.12819945211547</v>
+        <v>42.33914294561502</v>
       </c>
       <c r="P108" t="n">
         <v>277.44</v>
@@ -9101,18 +7809,6 @@
       </c>
       <c r="V108" t="n">
         <v>0.25</v>
-      </c>
-      <c r="W108" t="n">
-        <v>2</v>
-      </c>
-      <c r="X108" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y108" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z108" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="109">
@@ -9120,7 +7816,7 @@
         <v>107</v>
       </c>
       <c r="B109" t="n">
-        <v>674.8821413605247</v>
+        <v>749.8821413605247</v>
       </c>
       <c r="C109" t="n">
         <v>0</v>
@@ -9129,7 +7825,7 @@
         <v>0</v>
       </c>
       <c r="E109" t="n">
-        <v>487.3821413605247</v>
+        <v>562.3821413605247</v>
       </c>
       <c r="F109" t="n">
         <v>0</v>
@@ -9156,10 +7852,10 @@
         <v>6000</v>
       </c>
       <c r="N109" t="n">
-        <v>1090.515858639475</v>
+        <v>1015.515858639475</v>
       </c>
       <c r="O109" t="n">
-        <v>24.50046862816165</v>
+        <v>22.81545402470175</v>
       </c>
       <c r="P109" t="n">
         <v>278.03</v>
@@ -9181,18 +7877,6 @@
       </c>
       <c r="V109" t="n">
         <v>0.25</v>
-      </c>
-      <c r="W109" t="n">
-        <v>2</v>
-      </c>
-      <c r="X109" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y109" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z109" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="110">
@@ -9262,18 +7946,6 @@
       <c r="V110" t="n">
         <v>0.25</v>
       </c>
-      <c r="W110" t="n">
-        <v>2</v>
-      </c>
-      <c r="X110" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y110" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z110" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
@@ -9342,18 +8014,6 @@
       <c r="V111" t="n">
         <v>0.25</v>
       </c>
-      <c r="W111" t="n">
-        <v>2</v>
-      </c>
-      <c r="X111" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y111" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z111" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
@@ -9422,25 +8082,13 @@
       <c r="V112" t="n">
         <v>0.25</v>
       </c>
-      <c r="W112" t="n">
-        <v>2</v>
-      </c>
-      <c r="X112" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y112" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z112" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
         <v>111</v>
       </c>
       <c r="B113" t="n">
-        <v>892.960118015525</v>
+        <v>892.9601180155264</v>
       </c>
       <c r="C113" t="n">
         <v>0</v>
@@ -9449,7 +8097,7 @@
         <v>0</v>
       </c>
       <c r="E113" t="n">
-        <v>669.6850019764371</v>
+        <v>669.6850019764381</v>
       </c>
       <c r="F113" t="n">
         <v>0</v>
@@ -9458,7 +8106,7 @@
         <v>0</v>
       </c>
       <c r="H113" t="n">
-        <v>223.275116039088</v>
+        <v>223.2751160390883</v>
       </c>
       <c r="I113" t="n">
         <v>0</v>
@@ -9476,10 +8124,10 @@
         <v>6000</v>
       </c>
       <c r="N113" t="n">
-        <v>955.0177980235627</v>
+        <v>955.0177980235617</v>
       </c>
       <c r="O113" t="n">
-        <v>21.63672052388349</v>
+        <v>21.63672052388347</v>
       </c>
       <c r="P113" t="n">
         <v>278.36</v>
@@ -9501,18 +8149,6 @@
       </c>
       <c r="V113" t="n">
         <v>0.25</v>
-      </c>
-      <c r="W113" t="n">
-        <v>2</v>
-      </c>
-      <c r="X113" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y113" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z113" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="114">
@@ -9582,25 +8218,13 @@
       <c r="V114" t="n">
         <v>0.25</v>
       </c>
-      <c r="W114" t="n">
-        <v>2</v>
-      </c>
-      <c r="X114" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y114" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z114" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
         <v>113</v>
       </c>
       <c r="B115" t="n">
-        <v>878.8794856841756</v>
+        <v>878.8794856841762</v>
       </c>
       <c r="C115" t="n">
         <v>0</v>
@@ -9609,7 +8233,7 @@
         <v>0</v>
       </c>
       <c r="E115" t="n">
-        <v>640.3721340605088</v>
+        <v>640.3721340605092</v>
       </c>
       <c r="F115" t="n">
         <v>0</v>
@@ -9618,7 +8242,7 @@
         <v>0</v>
       </c>
       <c r="H115" t="n">
-        <v>238.5073516236669</v>
+        <v>238.507351623667</v>
       </c>
       <c r="I115" t="n">
         <v>0</v>
@@ -9636,10 +8260,10 @@
         <v>6000</v>
       </c>
       <c r="N115" t="n">
-        <v>905.6478659394912</v>
+        <v>905.6478659394908</v>
       </c>
       <c r="O115" t="n">
-        <v>20.41931945075229</v>
+        <v>20.41931945075228</v>
       </c>
       <c r="P115" t="n">
         <v>278.17</v>
@@ -9661,18 +8285,6 @@
       </c>
       <c r="V115" t="n">
         <v>0.25</v>
-      </c>
-      <c r="W115" t="n">
-        <v>2</v>
-      </c>
-      <c r="X115" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y115" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z115" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="116">
@@ -9742,25 +8354,13 @@
       <c r="V116" t="n">
         <v>0.25</v>
       </c>
-      <c r="W116" t="n">
-        <v>2</v>
-      </c>
-      <c r="X116" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y116" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z116" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
         <v>115</v>
       </c>
       <c r="B117" t="n">
-        <v>674.8821413605264</v>
+        <v>674.8821413605247</v>
       </c>
       <c r="C117" t="n">
         <v>0</v>
@@ -9769,7 +8369,7 @@
         <v>0</v>
       </c>
       <c r="E117" t="n">
-        <v>487.3821413605259</v>
+        <v>487.3821413605247</v>
       </c>
       <c r="F117" t="n">
         <v>0</v>
@@ -9778,7 +8378,7 @@
         <v>0</v>
       </c>
       <c r="H117" t="n">
-        <v>187.5000000000004</v>
+        <v>187.5</v>
       </c>
       <c r="I117" t="n">
         <v>0</v>
@@ -9796,10 +8396,10 @@
         <v>6000</v>
       </c>
       <c r="N117" t="n">
-        <v>964.6838586394741</v>
+        <v>964.6838586394754</v>
       </c>
       <c r="O117" t="n">
-        <v>21.7338445721248</v>
+        <v>21.73384457212483</v>
       </c>
       <c r="P117" t="n">
         <v>278.14</v>
@@ -9821,18 +8421,6 @@
       </c>
       <c r="V117" t="n">
         <v>0.25</v>
-      </c>
-      <c r="W117" t="n">
-        <v>2</v>
-      </c>
-      <c r="X117" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y117" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z117" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="118">
@@ -9840,7 +8428,7 @@
         <v>116</v>
       </c>
       <c r="B118" t="n">
-        <v>-1.250358696622815e-12</v>
+        <v>-3.374102790271704e-13</v>
       </c>
       <c r="C118" t="n">
         <v>0</v>
@@ -9849,7 +8437,7 @@
         <v>0</v>
       </c>
       <c r="E118" t="n">
-        <v>-9.377198928883705e-13</v>
+        <v>0</v>
       </c>
       <c r="F118" t="n">
         <v>0</v>
@@ -9858,7 +8446,7 @@
         <v>0</v>
       </c>
       <c r="H118" t="n">
-        <v>-3.126388037344441e-13</v>
+        <v>-3.374102790271704e-13</v>
       </c>
       <c r="I118" t="n">
         <v>0</v>
@@ -9876,10 +8464,10 @@
         <v>6000</v>
       </c>
       <c r="N118" t="n">
-        <v>1404.572400000001</v>
+        <v>1404.5724</v>
       </c>
       <c r="O118" t="n">
-        <v>31.50060048779122</v>
+        <v>31.5006004877912</v>
       </c>
       <c r="P118" t="n">
         <v>277.96</v>
@@ -9901,18 +8489,6 @@
       </c>
       <c r="V118" t="n">
         <v>0.25</v>
-      </c>
-      <c r="W118" t="n">
-        <v>2</v>
-      </c>
-      <c r="X118" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y118" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z118" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="119">
@@ -9920,7 +8496,7 @@
         <v>117</v>
       </c>
       <c r="B119" t="n">
-        <v>1206.448664344808</v>
+        <v>1184.624646729123</v>
       </c>
       <c r="C119" t="n">
         <v>0</v>
@@ -9929,7 +8505,7 @@
         <v>0</v>
       </c>
       <c r="E119" t="n">
-        <v>886.0361470807986</v>
+        <v>869.6689913867976</v>
       </c>
       <c r="F119" t="n">
         <v>0</v>
@@ -9938,7 +8514,7 @@
         <v>0</v>
       </c>
       <c r="H119" t="n">
-        <v>320.4125172640095</v>
+        <v>314.9556553423258</v>
       </c>
       <c r="I119" t="n">
         <v>0</v>
@@ -9956,10 +8532,10 @@
         <v>6000</v>
       </c>
       <c r="N119" t="n">
-        <v>495.0414529192012</v>
+        <v>511.4086086132022</v>
       </c>
       <c r="O119" t="n">
-        <v>10.97500796273691</v>
+        <v>11.33786578607626</v>
       </c>
       <c r="P119" t="n">
         <v>277.5</v>
@@ -9981,18 +8557,6 @@
       </c>
       <c r="V119" t="n">
         <v>0.16</v>
-      </c>
-      <c r="W119" t="n">
-        <v>2</v>
-      </c>
-      <c r="X119" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y119" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z119" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="120">
@@ -10062,18 +8626,6 @@
       <c r="V120" t="n">
         <v>0.16</v>
       </c>
-      <c r="W120" t="n">
-        <v>2</v>
-      </c>
-      <c r="X120" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y120" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z120" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
@@ -10142,25 +8694,13 @@
       <c r="V121" t="n">
         <v>0.16</v>
       </c>
-      <c r="W121" t="n">
-        <v>2</v>
-      </c>
-      <c r="X121" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y121" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z121" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
         <v>120</v>
       </c>
       <c r="B122" t="n">
-        <v>688.5220984488454</v>
+        <v>663.2801780127706</v>
       </c>
       <c r="C122" t="n">
         <v>0</v>
@@ -10169,7 +8709,7 @@
         <v>0</v>
       </c>
       <c r="E122" t="n">
-        <v>494.611442680593</v>
+        <v>475.7801780127706</v>
       </c>
       <c r="F122" t="n">
         <v>0</v>
@@ -10178,7 +8718,7 @@
         <v>0</v>
       </c>
       <c r="H122" t="n">
-        <v>193.9106557682525</v>
+        <v>187.5</v>
       </c>
       <c r="I122" t="n">
         <v>0</v>
@@ -10196,10 +8736,10 @@
         <v>6000</v>
       </c>
       <c r="N122" t="n">
-        <v>844.3737573194069</v>
+        <v>863.2050219872292</v>
       </c>
       <c r="O122" t="n">
-        <v>18.61289005443419</v>
+        <v>19.02799563512023</v>
       </c>
       <c r="P122" t="n">
         <v>277.27</v>
@@ -10221,18 +8761,6 @@
       </c>
       <c r="V122" t="n">
         <v>0.16</v>
-      </c>
-      <c r="W122" t="n">
-        <v>2</v>
-      </c>
-      <c r="X122" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y122" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z122" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="123">
@@ -10302,18 +8830,6 @@
       <c r="V123" t="n">
         <v>0.16</v>
       </c>
-      <c r="W123" t="n">
-        <v>2</v>
-      </c>
-      <c r="X123" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y123" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z123" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
@@ -10347,13 +8863,13 @@
         <v>0</v>
       </c>
       <c r="K124" t="n">
-        <v>2999.999999999997</v>
+        <v>3000</v>
       </c>
       <c r="L124" t="n">
-        <v>2399.999999999998</v>
+        <v>2400</v>
       </c>
       <c r="M124" t="n">
-        <v>5999.999999999994</v>
+        <v>6000</v>
       </c>
       <c r="N124" t="n">
         <v>1312.4832</v>
@@ -10381,18 +8897,6 @@
       </c>
       <c r="V124" t="n">
         <v>0.16</v>
-      </c>
-      <c r="W124" t="n">
-        <v>2</v>
-      </c>
-      <c r="X124" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y124" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z124" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="125">
@@ -10462,25 +8966,13 @@
       <c r="V125" t="n">
         <v>0.16</v>
       </c>
-      <c r="W125" t="n">
-        <v>2</v>
-      </c>
-      <c r="X125" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y125" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z125" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
         <v>124</v>
       </c>
       <c r="B126" t="n">
-        <v>-7.162260376816952e-12</v>
+        <v>738.2801780127706</v>
       </c>
       <c r="C126" t="n">
         <v>0</v>
@@ -10489,7 +8981,7 @@
         <v>0</v>
       </c>
       <c r="E126" t="n">
-        <v>-5.343270973271095e-12</v>
+        <v>550.7801780127706</v>
       </c>
       <c r="F126" t="n">
         <v>0</v>
@@ -10498,7 +8990,7 @@
         <v>0</v>
       </c>
       <c r="H126" t="n">
-        <v>-1.818989403545856e-12</v>
+        <v>187.5</v>
       </c>
       <c r="I126" t="n">
         <v>0</v>
@@ -10507,19 +8999,19 @@
         <v>0</v>
       </c>
       <c r="K126" t="n">
-        <v>3000.000000000004</v>
+        <v>3000</v>
       </c>
       <c r="L126" t="n">
-        <v>2400.000000000003</v>
+        <v>2400</v>
       </c>
       <c r="M126" t="n">
-        <v>6000.000000000008</v>
+        <v>6000</v>
       </c>
       <c r="N126" t="n">
-        <v>1282.117200000005</v>
+        <v>731.337021987229</v>
       </c>
       <c r="O126" t="n">
-        <v>28.17840000000011</v>
+        <v>16.07334114257646</v>
       </c>
       <c r="P126" t="n">
         <v>277.15</v>
@@ -10541,18 +9033,6 @@
       </c>
       <c r="V126" t="n">
         <v>0.16</v>
-      </c>
-      <c r="W126" t="n">
-        <v>2</v>
-      </c>
-      <c r="X126" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y126" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z126" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="127">
@@ -10560,7 +9040,7 @@
         <v>125</v>
       </c>
       <c r="B127" t="n">
-        <v>663.2801780127706</v>
+        <v>9.094947017729282e-13</v>
       </c>
       <c r="C127" t="n">
         <v>0</v>
@@ -10569,7 +9049,7 @@
         <v>0</v>
       </c>
       <c r="E127" t="n">
-        <v>475.7801780127706</v>
+        <v>9.094947017729282e-13</v>
       </c>
       <c r="F127" t="n">
         <v>0</v>
@@ -10578,7 +9058,7 @@
         <v>0</v>
       </c>
       <c r="H127" t="n">
-        <v>187.5</v>
+        <v>0</v>
       </c>
       <c r="I127" t="n">
         <v>0</v>
@@ -10596,10 +9076,10 @@
         <v>6000</v>
       </c>
       <c r="N127" t="n">
-        <v>821.8434219872292</v>
+        <v>1297.623599999999</v>
       </c>
       <c r="O127" t="n">
-        <v>18.04910471874664</v>
+        <v>28.49806132813572</v>
       </c>
       <c r="P127" t="n">
         <v>277.12</v>
@@ -10621,18 +9101,6 @@
       </c>
       <c r="V127" t="n">
         <v>0.16</v>
-      </c>
-      <c r="W127" t="n">
-        <v>2</v>
-      </c>
-      <c r="X127" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y127" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z127" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="128">
@@ -10640,7 +9108,7 @@
         <v>126</v>
       </c>
       <c r="B128" t="n">
-        <v>738.2801780127706</v>
+        <v>710.3461160645396</v>
       </c>
       <c r="C128" t="n">
         <v>0</v>
@@ -10649,7 +9117,7 @@
         <v>0</v>
       </c>
       <c r="E128" t="n">
-        <v>550.7801780127706</v>
+        <v>510.8928445999575</v>
       </c>
       <c r="F128" t="n">
         <v>0</v>
@@ -10658,7 +9126,7 @@
         <v>0</v>
       </c>
       <c r="H128" t="n">
-        <v>187.5</v>
+        <v>199.4532714645822</v>
       </c>
       <c r="I128" t="n">
         <v>0</v>
@@ -10676,10 +9144,10 @@
         <v>6000</v>
       </c>
       <c r="N128" t="n">
-        <v>741.4170219872294</v>
+        <v>781.3043554000426</v>
       </c>
       <c r="O128" t="n">
-        <v>16.28280170175375</v>
+        <v>17.15879661569809</v>
       </c>
       <c r="P128" t="n">
         <v>277.12</v>
@@ -10701,18 +9169,6 @@
       </c>
       <c r="V128" t="n">
         <v>0.16</v>
-      </c>
-      <c r="W128" t="n">
-        <v>2</v>
-      </c>
-      <c r="X128" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y128" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z128" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="129">
@@ -10720,7 +9176,7 @@
         <v>127</v>
       </c>
       <c r="B129" t="n">
-        <v>738.2801780127875</v>
+        <v>738.2801780127706</v>
       </c>
       <c r="C129" t="n">
         <v>0</v>
@@ -10729,7 +9185,7 @@
         <v>0</v>
       </c>
       <c r="E129" t="n">
-        <v>550.7801780127832</v>
+        <v>550.7801780127706</v>
       </c>
       <c r="F129" t="n">
         <v>0</v>
@@ -10738,7 +9194,7 @@
         <v>0</v>
       </c>
       <c r="H129" t="n">
-        <v>187.5000000000043</v>
+        <v>187.5</v>
       </c>
       <c r="I129" t="n">
         <v>0</v>
@@ -10756,10 +9212,10 @@
         <v>6000</v>
       </c>
       <c r="N129" t="n">
-        <v>767.1798219872169</v>
+        <v>767.1798219872294</v>
       </c>
       <c r="O129" t="n">
-        <v>16.81950829240266</v>
+        <v>16.81950829240294</v>
       </c>
       <c r="P129" t="n">
         <v>277.05</v>
@@ -10781,18 +9237,6 @@
       </c>
       <c r="V129" t="n">
         <v>0.16</v>
-      </c>
-      <c r="W129" t="n">
-        <v>2</v>
-      </c>
-      <c r="X129" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y129" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z129" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="130">
@@ -10862,18 +9306,6 @@
       <c r="V130" t="n">
         <v>0.25</v>
       </c>
-      <c r="W130" t="n">
-        <v>2</v>
-      </c>
-      <c r="X130" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y130" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z130" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
@@ -10942,18 +9374,6 @@
       <c r="V131" t="n">
         <v>0.25</v>
       </c>
-      <c r="W131" t="n">
-        <v>2</v>
-      </c>
-      <c r="X131" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y131" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z131" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
@@ -11022,18 +9442,6 @@
       <c r="V132" t="n">
         <v>0.25</v>
       </c>
-      <c r="W132" t="n">
-        <v>2</v>
-      </c>
-      <c r="X132" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y132" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z132" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
@@ -11102,18 +9510,6 @@
       <c r="V133" t="n">
         <v>0.25</v>
       </c>
-      <c r="W133" t="n">
-        <v>2</v>
-      </c>
-      <c r="X133" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y133" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z133" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
@@ -11182,18 +9578,6 @@
       <c r="V134" t="n">
         <v>0.25</v>
       </c>
-      <c r="W134" t="n">
-        <v>2</v>
-      </c>
-      <c r="X134" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y134" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z134" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
@@ -11262,25 +9646,13 @@
       <c r="V135" t="n">
         <v>0.25</v>
       </c>
-      <c r="W135" t="n">
-        <v>2</v>
-      </c>
-      <c r="X135" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y135" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z135" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
         <v>134</v>
       </c>
       <c r="B136" t="n">
-        <v>908.8157774552143</v>
+        <v>908.8157774552147</v>
       </c>
       <c r="C136" t="n">
         <v>0</v>
@@ -11289,7 +9661,7 @@
         <v>0</v>
       </c>
       <c r="E136" t="n">
-        <v>658.9574394332204</v>
+        <v>658.9574394332208</v>
       </c>
       <c r="F136" t="n">
         <v>0</v>
@@ -11298,7 +9670,7 @@
         <v>0</v>
       </c>
       <c r="H136" t="n">
-        <v>249.8583380219939</v>
+        <v>249.858338021994</v>
       </c>
       <c r="I136" t="n">
         <v>0</v>
@@ -11316,10 +9688,10 @@
         <v>6000</v>
       </c>
       <c r="N136" t="n">
-        <v>674.3997605667795</v>
+        <v>674.3997605667792</v>
       </c>
       <c r="O136" t="n">
-        <v>15.16697988455594</v>
+        <v>15.16697988455593</v>
       </c>
       <c r="P136" t="n">
         <v>278.07</v>
@@ -11341,18 +9713,6 @@
       </c>
       <c r="V136" t="n">
         <v>0.25</v>
-      </c>
-      <c r="W136" t="n">
-        <v>2</v>
-      </c>
-      <c r="X136" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y136" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z136" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="137">
@@ -11422,18 +9782,6 @@
       <c r="V137" t="n">
         <v>0.25</v>
       </c>
-      <c r="W137" t="n">
-        <v>2</v>
-      </c>
-      <c r="X137" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y137" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z137" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
@@ -11502,25 +9850,13 @@
       <c r="V138" t="n">
         <v>0.25</v>
       </c>
-      <c r="W138" t="n">
-        <v>2</v>
-      </c>
-      <c r="X138" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y138" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z138" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
         <v>137</v>
       </c>
       <c r="B139" t="n">
-        <v>663.2801780127648</v>
+        <v>663.2801780127706</v>
       </c>
       <c r="C139" t="n">
         <v>0</v>
@@ -11529,7 +9865,7 @@
         <v>0</v>
       </c>
       <c r="E139" t="n">
-        <v>475.7801780127663</v>
+        <v>475.7801780127706</v>
       </c>
       <c r="F139" t="n">
         <v>0</v>
@@ -11538,7 +9874,7 @@
         <v>0</v>
       </c>
       <c r="H139" t="n">
-        <v>187.4999999999985</v>
+        <v>187.5</v>
       </c>
       <c r="I139" t="n">
         <v>0</v>
@@ -11556,10 +9892,10 @@
         <v>6000</v>
       </c>
       <c r="N139" t="n">
-        <v>874.3350219872334</v>
+        <v>874.3350219872291</v>
       </c>
       <c r="O139" t="n">
-        <v>19.01865293354142</v>
+        <v>19.01865293354133</v>
       </c>
       <c r="P139" t="n">
         <v>276.73</v>
@@ -11581,18 +9917,6 @@
       </c>
       <c r="V139" t="n">
         <v>0.25</v>
-      </c>
-      <c r="W139" t="n">
-        <v>2</v>
-      </c>
-      <c r="X139" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y139" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z139" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="140">
@@ -11662,25 +9986,13 @@
       <c r="V140" t="n">
         <v>0.25</v>
       </c>
-      <c r="W140" t="n">
-        <v>2</v>
-      </c>
-      <c r="X140" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y140" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z140" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
         <v>139</v>
       </c>
       <c r="B141" t="n">
-        <v>738.2801780127725</v>
+        <v>738.2801780127706</v>
       </c>
       <c r="C141" t="n">
         <v>0</v>
@@ -11689,7 +10001,7 @@
         <v>0</v>
       </c>
       <c r="E141" t="n">
-        <v>550.780178012772</v>
+        <v>550.7801780127706</v>
       </c>
       <c r="F141" t="n">
         <v>0</v>
@@ -11698,7 +10010,7 @@
         <v>0</v>
       </c>
       <c r="H141" t="n">
-        <v>187.5000000000005</v>
+        <v>187.5</v>
       </c>
       <c r="I141" t="n">
         <v>0</v>
@@ -11716,10 +10028,10 @@
         <v>6000</v>
       </c>
       <c r="N141" t="n">
-        <v>786.9870219872278</v>
+        <v>786.9870219872291</v>
       </c>
       <c r="O141" t="n">
-        <v>16.8668689578531</v>
+        <v>16.86686895785313</v>
       </c>
       <c r="P141" t="n">
         <v>276.12</v>
@@ -11741,18 +10053,6 @@
       </c>
       <c r="V141" t="n">
         <v>0.25</v>
-      </c>
-      <c r="W141" t="n">
-        <v>2</v>
-      </c>
-      <c r="X141" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y141" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z141" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="142">
@@ -11822,25 +10122,13 @@
       <c r="V142" t="n">
         <v>0.25</v>
       </c>
-      <c r="W142" t="n">
-        <v>2</v>
-      </c>
-      <c r="X142" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y142" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z142" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
         <v>141</v>
       </c>
       <c r="B143" t="n">
-        <v>1187.163682357758</v>
+        <v>1187.163682357754</v>
       </c>
       <c r="C143" t="n">
         <v>0</v>
@@ -11849,7 +10137,7 @@
         <v>0</v>
       </c>
       <c r="E143" t="n">
-        <v>866.6137102874176</v>
+        <v>866.6137102874143</v>
       </c>
       <c r="F143" t="n">
         <v>0</v>
@@ -11858,7 +10146,7 @@
         <v>0</v>
       </c>
       <c r="H143" t="n">
-        <v>320.5499720703405</v>
+        <v>320.5499720703394</v>
       </c>
       <c r="I143" t="n">
         <v>0</v>
@@ -11876,10 +10164,10 @@
         <v>6000</v>
       </c>
       <c r="N143" t="n">
-        <v>428.7082897125823</v>
+        <v>428.7082897125856</v>
       </c>
       <c r="O143" t="n">
-        <v>9.109097547742849</v>
+        <v>9.109097547742918</v>
       </c>
       <c r="P143" t="n">
         <v>275.76</v>
@@ -11901,18 +10189,6 @@
       </c>
       <c r="V143" t="n">
         <v>0.16</v>
-      </c>
-      <c r="W143" t="n">
-        <v>2</v>
-      </c>
-      <c r="X143" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y143" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z143" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="144">
@@ -11982,18 +10258,6 @@
       <c r="V144" t="n">
         <v>0.16</v>
       </c>
-      <c r="W144" t="n">
-        <v>2</v>
-      </c>
-      <c r="X144" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y144" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z144" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
@@ -12062,18 +10326,6 @@
       <c r="V145" t="n">
         <v>0.16</v>
       </c>
-      <c r="W145" t="n">
-        <v>2</v>
-      </c>
-      <c r="X145" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y145" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z145" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
@@ -12142,18 +10394,6 @@
       <c r="V146" t="n">
         <v>0.16</v>
       </c>
-      <c r="W146" t="n">
-        <v>2</v>
-      </c>
-      <c r="X146" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y146" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z146" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
@@ -12222,18 +10462,6 @@
       <c r="V147" t="n">
         <v>0.16</v>
       </c>
-      <c r="W147" t="n">
-        <v>2</v>
-      </c>
-      <c r="X147" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y147" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z147" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
@@ -12302,18 +10530,6 @@
       <c r="V148" t="n">
         <v>0.16</v>
       </c>
-      <c r="W148" t="n">
-        <v>2</v>
-      </c>
-      <c r="X148" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y148" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z148" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
@@ -12382,18 +10598,6 @@
       <c r="V149" t="n">
         <v>0.16</v>
       </c>
-      <c r="W149" t="n">
-        <v>2</v>
-      </c>
-      <c r="X149" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y149" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z149" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
@@ -12462,18 +10666,6 @@
       <c r="V150" t="n">
         <v>0.16</v>
       </c>
-      <c r="W150" t="n">
-        <v>2</v>
-      </c>
-      <c r="X150" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y150" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z150" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
@@ -12542,25 +10734,13 @@
       <c r="V151" t="n">
         <v>0.16</v>
       </c>
-      <c r="W151" t="n">
-        <v>2</v>
-      </c>
-      <c r="X151" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y151" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z151" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
         <v>150</v>
       </c>
       <c r="B152" t="n">
-        <v>840.8406264764045</v>
+        <v>830.7139884371149</v>
       </c>
       <c r="C152" t="n">
         <v>0</v>
@@ -12569,7 +10749,7 @@
         <v>0</v>
       </c>
       <c r="E152" t="n">
-        <v>624.9557164321141</v>
+        <v>617.4290816197433</v>
       </c>
       <c r="F152" t="n">
         <v>0</v>
@@ -12578,7 +10758,7 @@
         <v>0</v>
       </c>
       <c r="H152" t="n">
-        <v>215.8849100442905</v>
+        <v>213.2849068173716</v>
       </c>
       <c r="I152" t="n">
         <v>0</v>
@@ -12596,10 +10776,10 @@
         <v>6000</v>
       </c>
       <c r="N152" t="n">
-        <v>661.3614835678857</v>
+        <v>668.8881183802564</v>
       </c>
       <c r="O152" t="n">
-        <v>13.68605465362034</v>
+        <v>13.84180901482721</v>
       </c>
       <c r="P152" t="n">
         <v>274.64</v>
@@ -12621,18 +10801,6 @@
       </c>
       <c r="V152" t="n">
         <v>0.16</v>
-      </c>
-      <c r="W152" t="n">
-        <v>2</v>
-      </c>
-      <c r="X152" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y152" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z152" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="153">
@@ -12640,7 +10808,7 @@
         <v>151</v>
       </c>
       <c r="B153" t="n">
-        <v>1460.570981380598</v>
+        <v>1460.570981380599</v>
       </c>
       <c r="C153" t="n">
         <v>0</v>
@@ -12658,7 +10826,7 @@
         <v>0</v>
       </c>
       <c r="H153" t="n">
-        <v>374.9999999999998</v>
+        <v>375</v>
       </c>
       <c r="I153" t="n">
         <v>0</v>
@@ -12676,10 +10844,10 @@
         <v>6000</v>
       </c>
       <c r="N153" t="n">
-        <v>214.4802186194011</v>
+        <v>214.4802186194006</v>
       </c>
       <c r="O153" t="n">
-        <v>4.443574219079115</v>
+        <v>4.443574219079105</v>
       </c>
       <c r="P153" t="n">
         <v>274.69</v>
@@ -12701,18 +10869,6 @@
       </c>
       <c r="V153" t="n">
         <v>0.16</v>
-      </c>
-      <c r="W153" t="n">
-        <v>2</v>
-      </c>
-      <c r="X153" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y153" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z153" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="154">
@@ -12720,7 +10876,7 @@
         <v>152</v>
       </c>
       <c r="B154" t="n">
-        <v>836.3385825111396</v>
+        <v>730.2854906902991</v>
       </c>
       <c r="C154" t="n">
         <v>0</v>
@@ -12729,7 +10885,7 @@
         <v>0</v>
       </c>
       <c r="E154" t="n">
-        <v>621.6095673247481</v>
+        <v>542.7854906902992</v>
       </c>
       <c r="F154" t="n">
         <v>0</v>
@@ -12738,7 +10894,7 @@
         <v>0</v>
       </c>
       <c r="H154" t="n">
-        <v>214.7290151863915</v>
+        <v>187.4999999999999</v>
       </c>
       <c r="I154" t="n">
         <v>0</v>
@@ -12756,10 +10912,10 @@
         <v>6000</v>
       </c>
       <c r="N154" t="n">
-        <v>660.2556326752518</v>
+        <v>739.0797093097008</v>
       </c>
       <c r="O154" t="n">
-        <v>13.64728467704117</v>
+        <v>15.27655455373503</v>
       </c>
       <c r="P154" t="n">
         <v>274.59</v>
@@ -12781,18 +10937,6 @@
       </c>
       <c r="V154" t="n">
         <v>0.25</v>
-      </c>
-      <c r="W154" t="n">
-        <v>2</v>
-      </c>
-      <c r="X154" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y154" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z154" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="155">
@@ -12800,7 +10944,7 @@
         <v>153</v>
       </c>
       <c r="B155" t="n">
-        <v>0</v>
+        <v>730.2854906902995</v>
       </c>
       <c r="C155" t="n">
         <v>0</v>
@@ -12809,7 +10953,7 @@
         <v>0</v>
       </c>
       <c r="E155" t="n">
-        <v>0</v>
+        <v>542.7854906902995</v>
       </c>
       <c r="F155" t="n">
         <v>0</v>
@@ -12818,7 +10962,7 @@
         <v>0</v>
       </c>
       <c r="H155" t="n">
-        <v>0</v>
+        <v>187.5</v>
       </c>
       <c r="I155" t="n">
         <v>0</v>
@@ -12836,10 +10980,10 @@
         <v>6000</v>
       </c>
       <c r="N155" t="n">
-        <v>1281</v>
+        <v>738.2145093097005</v>
       </c>
       <c r="O155" t="n">
-        <v>26.89693183905935</v>
+        <v>15.50016029625891</v>
       </c>
       <c r="P155" t="n">
         <v>275.26</v>
@@ -12861,18 +11005,6 @@
       </c>
       <c r="V155" t="n">
         <v>0.25</v>
-      </c>
-      <c r="W155" t="n">
-        <v>2</v>
-      </c>
-      <c r="X155" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y155" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z155" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="156">
@@ -12880,7 +11012,7 @@
         <v>154</v>
       </c>
       <c r="B156" t="n">
-        <v>655.2854906902995</v>
+        <v>0</v>
       </c>
       <c r="C156" t="n">
         <v>0</v>
@@ -12889,7 +11021,7 @@
         <v>0</v>
       </c>
       <c r="E156" t="n">
-        <v>467.7854906902995</v>
+        <v>0</v>
       </c>
       <c r="F156" t="n">
         <v>0</v>
@@ -12898,7 +11030,7 @@
         <v>0</v>
       </c>
       <c r="H156" t="n">
-        <v>187.5</v>
+        <v>0</v>
       </c>
       <c r="I156" t="n">
         <v>0</v>
@@ -12916,10 +11048,10 @@
         <v>6000</v>
       </c>
       <c r="N156" t="n">
-        <v>826.3353093097004</v>
+        <v>1294.1208</v>
       </c>
       <c r="O156" t="n">
-        <v>17.53264149178519</v>
+        <v>27.45780771780932</v>
       </c>
       <c r="P156" t="n">
         <v>275.7</v>
@@ -12941,18 +11073,6 @@
       </c>
       <c r="V156" t="n">
         <v>0.25</v>
-      </c>
-      <c r="W156" t="n">
-        <v>2</v>
-      </c>
-      <c r="X156" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y156" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z156" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="157">
@@ -12960,7 +11080,7 @@
         <v>155</v>
       </c>
       <c r="B157" t="n">
-        <v>869.1593581332944</v>
+        <v>655.2854906902995</v>
       </c>
       <c r="C157" t="n">
         <v>0</v>
@@ -12969,7 +11089,7 @@
         <v>0</v>
       </c>
       <c r="E157" t="n">
-        <v>646.0036447479054</v>
+        <v>467.7854906902995</v>
       </c>
       <c r="F157" t="n">
         <v>0</v>
@@ -12978,7 +11098,7 @@
         <v>0</v>
       </c>
       <c r="H157" t="n">
-        <v>223.155713385389</v>
+        <v>187.5</v>
       </c>
       <c r="I157" t="n">
         <v>0</v>
@@ -12996,10 +11116,10 @@
         <v>6000</v>
       </c>
       <c r="N157" t="n">
-        <v>640.7167552520943</v>
+        <v>818.9349093097002</v>
       </c>
       <c r="O157" t="n">
-        <v>13.78849206977122</v>
+        <v>17.62382115047506</v>
       </c>
       <c r="P157" t="n">
         <v>276.29</v>
@@ -13021,18 +11141,6 @@
       </c>
       <c r="V157" t="n">
         <v>0.25</v>
-      </c>
-      <c r="W157" t="n">
-        <v>2</v>
-      </c>
-      <c r="X157" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y157" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z157" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="158">
@@ -13040,7 +11148,7 @@
         <v>156</v>
       </c>
       <c r="B158" t="n">
-        <v>0</v>
+        <v>730.2854906902995</v>
       </c>
       <c r="C158" t="n">
         <v>0</v>
@@ -13049,7 +11157,7 @@
         <v>0</v>
       </c>
       <c r="E158" t="n">
-        <v>0</v>
+        <v>542.7854906902995</v>
       </c>
       <c r="F158" t="n">
         <v>0</v>
@@ -13058,7 +11166,7 @@
         <v>0</v>
       </c>
       <c r="H158" t="n">
-        <v>0</v>
+        <v>187.5</v>
       </c>
       <c r="I158" t="n">
         <v>0</v>
@@ -13076,10 +11184,10 @@
         <v>6000</v>
       </c>
       <c r="N158" t="n">
-        <v>1295.196</v>
+        <v>752.4105093097004</v>
       </c>
       <c r="O158" t="n">
-        <v>28.05655952993422</v>
+        <v>16.29873026584064</v>
       </c>
       <c r="P158" t="n">
         <v>276.56</v>
@@ -13101,18 +11209,6 @@
       </c>
       <c r="V158" t="n">
         <v>0.25</v>
-      </c>
-      <c r="W158" t="n">
-        <v>2</v>
-      </c>
-      <c r="X158" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y158" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z158" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="159">
@@ -13182,18 +11278,6 @@
       <c r="V159" t="n">
         <v>0.25</v>
       </c>
-      <c r="W159" t="n">
-        <v>2</v>
-      </c>
-      <c r="X159" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y159" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z159" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
@@ -13262,25 +11346,13 @@
       <c r="V160" t="n">
         <v>0.25</v>
       </c>
-      <c r="W160" t="n">
-        <v>2</v>
-      </c>
-      <c r="X160" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y160" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z160" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
         <v>159</v>
       </c>
       <c r="B161" t="n">
-        <v>936.3516714746185</v>
+        <v>0</v>
       </c>
       <c r="C161" t="n">
         <v>0</v>
@@ -13289,7 +11361,7 @@
         <v>0</v>
       </c>
       <c r="E161" t="n">
-        <v>676.6882373534703</v>
+        <v>0</v>
       </c>
       <c r="F161" t="n">
         <v>0</v>
@@ -13298,7 +11370,7 @@
         <v>0</v>
       </c>
       <c r="H161" t="n">
-        <v>259.6634341211482</v>
+        <v>0</v>
       </c>
       <c r="I161" t="n">
         <v>0</v>
@@ -13316,10 +11388,10 @@
         <v>6000</v>
       </c>
       <c r="N161" t="n">
-        <v>611.8969626465297</v>
+        <v>1288.5852</v>
       </c>
       <c r="O161" t="n">
-        <v>13.40189372275157</v>
+        <v>28.22285933307782</v>
       </c>
       <c r="P161" t="n">
         <v>277.01</v>
@@ -13341,18 +11413,6 @@
       </c>
       <c r="V161" t="n">
         <v>0.25</v>
-      </c>
-      <c r="W161" t="n">
-        <v>2</v>
-      </c>
-      <c r="X161" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y161" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z161" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="162">
@@ -13422,25 +11482,13 @@
       <c r="V162" t="n">
         <v>0.25</v>
       </c>
-      <c r="W162" t="n">
-        <v>2</v>
-      </c>
-      <c r="X162" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y162" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z162" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
         <v>161</v>
       </c>
       <c r="B163" t="n">
-        <v>5.383810838882299e-13</v>
+        <v>655.2854906902995</v>
       </c>
       <c r="C163" t="n">
         <v>0</v>
@@ -13449,7 +11497,7 @@
         <v>0</v>
       </c>
       <c r="E163" t="n">
-        <v>0</v>
+        <v>467.7854906902995</v>
       </c>
       <c r="F163" t="n">
         <v>0</v>
@@ -13458,7 +11506,7 @@
         <v>0</v>
       </c>
       <c r="H163" t="n">
-        <v>5.383810838882299e-13</v>
+        <v>187.5</v>
       </c>
       <c r="I163" t="n">
         <v>0</v>
@@ -13476,10 +11524,10 @@
         <v>6000</v>
       </c>
       <c r="N163" t="n">
-        <v>1293.3144</v>
+        <v>825.5289093097002</v>
       </c>
       <c r="O163" t="n">
-        <v>27.23914069081718</v>
+        <v>17.38687677568872</v>
       </c>
       <c r="P163" t="n">
         <v>275.39</v>
@@ -13501,18 +11549,6 @@
       </c>
       <c r="V163" t="n">
         <v>0.25</v>
-      </c>
-      <c r="W163" t="n">
-        <v>2</v>
-      </c>
-      <c r="X163" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y163" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z163" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="164">
@@ -13520,7 +11556,7 @@
         <v>162</v>
       </c>
       <c r="B164" t="n">
-        <v>662.4149293882379</v>
+        <v>730.2854906902995</v>
       </c>
       <c r="C164" t="n">
         <v>0</v>
@@ -13529,7 +11565,7 @@
         <v>0</v>
       </c>
       <c r="E164" t="n">
-        <v>473.0844538099817</v>
+        <v>542.7854906902995</v>
       </c>
       <c r="F164" t="n">
         <v>0</v>
@@ -13538,7 +11574,7 @@
         <v>0</v>
       </c>
       <c r="H164" t="n">
-        <v>189.3304755782562</v>
+        <v>187.5</v>
       </c>
       <c r="I164" t="n">
         <v>0</v>
@@ -13556,10 +11592,10 @@
         <v>6000</v>
       </c>
       <c r="N164" t="n">
-        <v>827.3363461900179</v>
+        <v>757.6353093097001</v>
       </c>
       <c r="O164" t="n">
-        <v>17.13266403375476</v>
+        <v>15.68927954669082</v>
       </c>
       <c r="P164" t="n">
         <v>274.67</v>
@@ -13581,18 +11617,6 @@
       </c>
       <c r="V164" t="n">
         <v>0.25</v>
-      </c>
-      <c r="W164" t="n">
-        <v>2</v>
-      </c>
-      <c r="X164" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y164" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z164" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="165">
@@ -13662,18 +11686,6 @@
       <c r="V165" t="n">
         <v>0.25</v>
       </c>
-      <c r="W165" t="n">
-        <v>2</v>
-      </c>
-      <c r="X165" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y165" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z165" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
@@ -13742,25 +11754,13 @@
       <c r="V166" t="n">
         <v>0.25</v>
       </c>
-      <c r="W166" t="n">
-        <v>2</v>
-      </c>
-      <c r="X166" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y166" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z166" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
         <v>165</v>
       </c>
       <c r="B167" t="n">
-        <v>1207.976844833663</v>
+        <v>945.9405709287453</v>
       </c>
       <c r="C167" t="n">
         <v>0</v>
@@ -13769,7 +11769,7 @@
         <v>0</v>
       </c>
       <c r="E167" t="n">
-        <v>897.8301127765632</v>
+        <v>703.071365241135</v>
       </c>
       <c r="F167" t="n">
         <v>0</v>
@@ -13778,7 +11778,7 @@
         <v>0</v>
       </c>
       <c r="H167" t="n">
-        <v>310.1467320570995</v>
+        <v>242.8692056876102</v>
       </c>
       <c r="I167" t="n">
         <v>0</v>
@@ -13796,10 +11796,10 @@
         <v>6000</v>
       </c>
       <c r="N167" t="n">
-        <v>410.6798872234368</v>
+        <v>605.438634758865</v>
       </c>
       <c r="O167" t="n">
-        <v>8.252591238068607</v>
+        <v>12.16625826548169</v>
       </c>
       <c r="P167" t="n">
         <v>273.36</v>
@@ -13821,18 +11821,6 @@
       </c>
       <c r="V167" t="n">
         <v>0.16</v>
-      </c>
-      <c r="W167" t="n">
-        <v>2</v>
-      </c>
-      <c r="X167" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y167" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z167" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="168">
@@ -13902,18 +11890,6 @@
       <c r="V168" t="n">
         <v>0.16</v>
       </c>
-      <c r="W168" t="n">
-        <v>2</v>
-      </c>
-      <c r="X168" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y168" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z168" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
@@ -13982,20 +11958,8 @@
       <c r="V169" t="n">
         <v>0.16</v>
       </c>
-      <c r="W169" t="n">
-        <v>2</v>
-      </c>
-      <c r="X169" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y169" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z169" t="n">
-        <v>1</v>
-      </c>
     </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>